--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>131292182</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292162</v>
+        <v>131292184</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,31 +1347,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528917</v>
+        <v>528962</v>
       </c>
       <c r="R7" t="n">
-        <v>7000356</v>
+        <v>7000560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,12 +1423,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1446,14 +1442,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1471,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292254</v>
+        <v>131292188</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,31 +1473,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1514,10 +1500,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529159</v>
+        <v>528907</v>
       </c>
       <c r="R8" t="n">
-        <v>7000453</v>
+        <v>7000430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,7 +1540,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1563,6 +1549,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1581,9 +1568,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1601,10 +1593,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292184</v>
+        <v>131292273</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1639,10 +1631,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528962</v>
+        <v>528941</v>
       </c>
       <c r="R9" t="n">
-        <v>7000560</v>
+        <v>7000481</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1675,11 +1667,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1727,10 +1714,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292188</v>
+        <v>131292162</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,26 +1725,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1765,10 +1757,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528907</v>
+        <v>528917</v>
       </c>
       <c r="R10" t="n">
-        <v>7000430</v>
+        <v>7000356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1805,7 +1797,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,13 +1806,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1835,12 +1826,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1858,10 +1849,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292273</v>
+        <v>131292254</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,26 +1860,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1896,10 +1892,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528941</v>
+        <v>529159</v>
       </c>
       <c r="R11" t="n">
-        <v>7000481</v>
+        <v>7000453</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1934,13 +1930,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>131292270</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131292183</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>131292186</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>131292181</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>131292185</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>131292191</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292163</v>
+        <v>131292265</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>79003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2851,31 +2851,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2883,10 +2878,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528921</v>
+        <v>529126</v>
       </c>
       <c r="R19" t="n">
-        <v>7000354</v>
+        <v>7000447</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2921,43 +2916,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2975,10 +2946,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292265</v>
+        <v>131292263</v>
       </c>
       <c r="B20" t="n">
-        <v>79002</v>
+        <v>80351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2986,26 +2957,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3013,10 +2988,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529126</v>
+        <v>528966</v>
       </c>
       <c r="R20" t="n">
-        <v>7000447</v>
+        <v>7000477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3051,6 +3026,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3064,6 +3044,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292263</v>
+        <v>131292163</v>
       </c>
       <c r="B21" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,28 +3092,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3123,10 +3124,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528966</v>
+        <v>528921</v>
       </c>
       <c r="R21" t="n">
-        <v>7000477</v>
+        <v>7000354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3163,7 +3164,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3172,7 +3173,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3183,22 +3183,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3477,7 +3477,7 @@
         <v>131292274</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>131292271</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131292190</v>
+        <v>131292170</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3862,26 +3862,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3889,10 +3893,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528945</v>
+        <v>528917</v>
       </c>
       <c r="R27" t="n">
-        <v>7000349</v>
+        <v>7000532</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3927,11 +3931,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På flera granar i klenvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3944,22 +3943,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3977,10 +3981,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131292170</v>
+        <v>131292190</v>
       </c>
       <c r="B28" t="n">
-        <v>80350</v>
+        <v>79246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3988,30 +3992,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528917</v>
+        <v>528945</v>
       </c>
       <c r="R28" t="n">
-        <v>7000532</v>
+        <v>7000349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4057,6 +4057,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På flera granar i klenvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4069,27 +4074,22 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4110,7 +4110,7 @@
         <v>131292264</v>
       </c>
       <c r="B29" t="n">
-        <v>78257</v>
+        <v>78258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292249</v>
+        <v>131292166</v>
       </c>
       <c r="B30" t="n">
-        <v>83225</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4244,26 +4244,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4271,10 +4276,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528960</v>
+        <v>528920</v>
       </c>
       <c r="R30" t="n">
-        <v>7000493</v>
+        <v>7000269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4309,19 +4314,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4334,9 +4343,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4354,7 +4368,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292166</v>
+        <v>131292160</v>
       </c>
       <c r="B31" t="n">
         <v>57884</v>
@@ -4387,7 +4401,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4397,10 +4411,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528920</v>
+        <v>528916</v>
       </c>
       <c r="R31" t="n">
-        <v>7000269</v>
+        <v>7000358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4437,7 +4451,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4451,7 +4465,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4489,7 +4503,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292160</v>
+        <v>131292157</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4522,7 +4536,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4532,10 +4546,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528916</v>
+        <v>528904</v>
       </c>
       <c r="R32" t="n">
-        <v>7000358</v>
+        <v>7000487</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4572,7 +4586,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4624,10 +4638,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292157</v>
+        <v>131292249</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>83226</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4635,31 +4649,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4667,10 +4676,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528904</v>
+        <v>528960</v>
       </c>
       <c r="R33" t="n">
-        <v>7000487</v>
+        <v>7000493</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4705,23 +4714,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4734,14 +4739,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131292192</v>
+        <v>131292159</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4905,26 +4905,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4932,10 +4937,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528927</v>
+        <v>528913</v>
       </c>
       <c r="R35" t="n">
-        <v>7000269</v>
+        <v>7000365</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4972,7 +4977,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i tallskog.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4981,13 +4986,12 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5000,9 +5004,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5020,10 +5029,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131292187</v>
+        <v>131292192</v>
       </c>
       <c r="B36" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5058,10 +5067,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528912</v>
+        <v>528927</v>
       </c>
       <c r="R36" t="n">
-        <v>7000471</v>
+        <v>7000269</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5098,7 +5107,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Bland andra hänglavar på gran i tallskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5113,7 +5122,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5146,10 +5155,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131292159</v>
+        <v>131292187</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5157,31 +5166,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5189,10 +5193,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528913</v>
+        <v>528912</v>
       </c>
       <c r="R37" t="n">
-        <v>7000365</v>
+        <v>7000471</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5229,7 +5233,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5238,6 +5242,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5256,14 +5261,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5284,7 +5284,7 @@
         <v>131292267</v>
       </c>
       <c r="B38" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>131292189</v>
       </c>
       <c r="B39" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -4894,10 +4894,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131292159</v>
+        <v>131292192</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4905,31 +4905,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4937,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528913</v>
+        <v>528927</v>
       </c>
       <c r="R35" t="n">
-        <v>7000365</v>
+        <v>7000269</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4977,7 +4972,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Bland andra hänglavar på gran i tallskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4986,12 +4981,13 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5004,14 +5000,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5029,7 +5020,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131292192</v>
+        <v>131292187</v>
       </c>
       <c r="B36" t="n">
         <v>79246</v>
@@ -5067,10 +5058,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528927</v>
+        <v>528912</v>
       </c>
       <c r="R36" t="n">
-        <v>7000269</v>
+        <v>7000471</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5107,7 +5098,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i tallskog.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5122,7 +5113,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5155,10 +5146,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131292187</v>
+        <v>131292159</v>
       </c>
       <c r="B37" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5166,26 +5157,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5193,10 +5189,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528912</v>
+        <v>528913</v>
       </c>
       <c r="R37" t="n">
-        <v>7000471</v>
+        <v>7000365</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5233,7 +5229,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5242,7 +5238,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5261,9 +5256,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292161</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292257</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131292153</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>131292255</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292182</v>
+        <v>131292188</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528964</v>
+        <v>528907</v>
       </c>
       <c r="R6" t="n">
-        <v>7000504</v>
+        <v>7000430</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,9 +1316,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1336,10 +1341,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292184</v>
+        <v>131292182</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528962</v>
+        <v>528964</v>
       </c>
       <c r="R7" t="n">
-        <v>7000560</v>
+        <v>7000504</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1419,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1462,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292188</v>
+        <v>131292184</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,10 +1505,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528907</v>
+        <v>528962</v>
       </c>
       <c r="R8" t="n">
-        <v>7000430</v>
+        <v>7000560</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,7 +1545,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,14 +1573,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
         <v>131292273</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>131292162</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>131292254</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>131292270</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131292183</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131292149</v>
       </c>
       <c r="B14" t="n">
-        <v>56699</v>
+        <v>56701</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>131292186</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>131292181</v>
       </c>
       <c r="B16" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>131292185</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>131292191</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>131292265</v>
       </c>
       <c r="B19" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>131292263</v>
       </c>
       <c r="B20" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>131292163</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>131292256</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>131292260</v>
       </c>
       <c r="B23" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>131292274</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>131292271</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>131292165</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>131292170</v>
       </c>
       <c r="B27" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>131292190</v>
       </c>
       <c r="B28" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292264</v>
+        <v>131292249</v>
       </c>
       <c r="B29" t="n">
-        <v>78258</v>
+        <v>83228</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,21 +4118,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528951</v>
+        <v>528960</v>
       </c>
       <c r="R29" t="n">
-        <v>7000496</v>
+        <v>7000493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4208,14 +4208,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4236,7 +4231,7 @@
         <v>131292166</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4371,7 +4366,7 @@
         <v>131292160</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4506,7 +4501,7 @@
         <v>131292157</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4638,10 +4633,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292249</v>
+        <v>131292264</v>
       </c>
       <c r="B33" t="n">
-        <v>83226</v>
+        <v>78260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4649,21 +4644,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4676,10 +4671,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528960</v>
+        <v>528951</v>
       </c>
       <c r="R33" t="n">
-        <v>7000493</v>
+        <v>7000496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4726,7 +4721,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4739,9 +4734,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,7 +4762,7 @@
         <v>131292164</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>131292192</v>
       </c>
       <c r="B35" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>131292187</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>131292159</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>131292267</v>
       </c>
       <c r="B38" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>131292189</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131292161</v>
+        <v>131292257</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528920</v>
+        <v>528915</v>
       </c>
       <c r="R2" t="n">
-        <v>7000358</v>
+        <v>7000264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,14 +785,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292257</v>
+        <v>131292161</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -843,7 +838,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528915</v>
+        <v>528920</v>
       </c>
       <c r="R3" t="n">
-        <v>7000264</v>
+        <v>7000358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,9 +915,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,7 +943,7 @@
         <v>131292153</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>131292255</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292188</v>
+        <v>131292182</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528907</v>
+        <v>528964</v>
       </c>
       <c r="R6" t="n">
-        <v>7000430</v>
+        <v>7000504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,14 +1316,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1341,10 +1336,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292182</v>
+        <v>131292184</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528964</v>
+        <v>528962</v>
       </c>
       <c r="R7" t="n">
-        <v>7000504</v>
+        <v>7000560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292184</v>
+        <v>131292188</v>
       </c>
       <c r="B8" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,10 +1500,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528962</v>
+        <v>528907</v>
       </c>
       <c r="R8" t="n">
-        <v>7000560</v>
+        <v>7000430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1545,7 +1540,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,9 +1568,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
         <v>131292273</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>131292162</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>131292254</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>131292270</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131292183</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131292149</v>
       </c>
       <c r="B14" t="n">
-        <v>56701</v>
+        <v>56702</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>131292186</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>131292181</v>
       </c>
       <c r="B16" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>131292185</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292191</v>
+        <v>131292163</v>
       </c>
       <c r="B18" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,26 +2725,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2752,10 +2757,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528927</v>
+        <v>528921</v>
       </c>
       <c r="R18" t="n">
-        <v>7000340</v>
+        <v>7000354</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2792,7 +2797,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2801,7 +2806,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2820,9 +2824,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2840,10 +2849,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292265</v>
+        <v>131292191</v>
       </c>
       <c r="B19" t="n">
-        <v>79005</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2851,21 +2860,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2878,10 +2887,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529126</v>
+        <v>528927</v>
       </c>
       <c r="R19" t="n">
-        <v>7000447</v>
+        <v>7000340</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2916,6 +2925,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2929,6 +2943,21 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2946,10 +2975,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292263</v>
+        <v>131292265</v>
       </c>
       <c r="B20" t="n">
-        <v>80353</v>
+        <v>79006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,30 +2986,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2988,10 +3013,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528966</v>
+        <v>529126</v>
       </c>
       <c r="R20" t="n">
-        <v>7000477</v>
+        <v>7000447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3026,11 +3051,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3044,26 +3064,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292163</v>
+        <v>131292263</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,29 +3092,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3124,10 +3123,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528921</v>
+        <v>528966</v>
       </c>
       <c r="R21" t="n">
-        <v>7000354</v>
+        <v>7000477</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3164,7 +3163,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3173,6 +3172,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3183,22 +3183,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
         <v>131292256</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>131292260</v>
       </c>
       <c r="B23" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131292274</v>
+        <v>131292165</v>
       </c>
       <c r="B24" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3485,26 +3485,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3512,10 +3517,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528983</v>
+        <v>528924</v>
       </c>
       <c r="R24" t="n">
-        <v>7000463</v>
+        <v>7000345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3550,13 +3555,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3575,9 +3584,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3595,10 +3609,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131292271</v>
+        <v>131292274</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3633,10 +3647,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529122</v>
+        <v>528983</v>
       </c>
       <c r="R25" t="n">
-        <v>7000459</v>
+        <v>7000463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3716,10 +3730,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131292165</v>
+        <v>131292271</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3727,31 +3741,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3759,10 +3768,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528924</v>
+        <v>529122</v>
       </c>
       <c r="R26" t="n">
-        <v>7000345</v>
+        <v>7000459</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3797,17 +3806,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3826,14 +3831,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3854,7 +3854,7 @@
         <v>131292170</v>
       </c>
       <c r="B27" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>131292190</v>
       </c>
       <c r="B28" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>131292249</v>
       </c>
       <c r="B29" t="n">
-        <v>83228</v>
+        <v>83229</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292166</v>
+        <v>131292160</v>
       </c>
       <c r="B30" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528920</v>
+        <v>528916</v>
       </c>
       <c r="R30" t="n">
-        <v>7000269</v>
+        <v>7000358</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4363,10 +4363,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292160</v>
+        <v>131292166</v>
       </c>
       <c r="B31" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528916</v>
+        <v>528920</v>
       </c>
       <c r="R31" t="n">
-        <v>7000358</v>
+        <v>7000269</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4501,7 +4501,7 @@
         <v>131292157</v>
       </c>
       <c r="B32" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>131292264</v>
       </c>
       <c r="B33" t="n">
-        <v>78260</v>
+        <v>78261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>131292164</v>
       </c>
       <c r="B34" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>131292192</v>
       </c>
       <c r="B35" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>131292187</v>
       </c>
       <c r="B36" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>131292159</v>
       </c>
       <c r="B37" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>131292267</v>
       </c>
       <c r="B38" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>131292189</v>
       </c>
       <c r="B39" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131292257</v>
+        <v>131292161</v>
       </c>
       <c r="B2" t="n">
         <v>57887</v>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528915</v>
+        <v>528920</v>
       </c>
       <c r="R2" t="n">
-        <v>7000264</v>
+        <v>7000358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,9 +785,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292161</v>
+        <v>131292257</v>
       </c>
       <c r="B3" t="n">
         <v>57887</v>
@@ -838,7 +843,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528920</v>
+        <v>528915</v>
       </c>
       <c r="R3" t="n">
-        <v>7000358</v>
+        <v>7000264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,14 +920,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292182</v>
+        <v>131292162</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,26 +1221,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528964</v>
+        <v>528917</v>
       </c>
       <c r="R6" t="n">
-        <v>7000504</v>
+        <v>7000356</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,7 +1293,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,13 +1302,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1316,9 +1320,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1336,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292184</v>
+        <v>131292254</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,26 +1356,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1374,10 +1388,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528962</v>
+        <v>529159</v>
       </c>
       <c r="R7" t="n">
-        <v>7000560</v>
+        <v>7000453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1428,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,7 +1437,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1462,7 +1475,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292188</v>
+        <v>131292182</v>
       </c>
       <c r="B8" t="n">
         <v>79249</v>
@@ -1500,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528907</v>
+        <v>528964</v>
       </c>
       <c r="R8" t="n">
-        <v>7000430</v>
+        <v>7000504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,7 +1553,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,14 +1581,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1593,7 +1601,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292273</v>
+        <v>131292184</v>
       </c>
       <c r="B9" t="n">
         <v>79249</v>
@@ -1631,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528941</v>
+        <v>528962</v>
       </c>
       <c r="R9" t="n">
-        <v>7000481</v>
+        <v>7000560</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1667,6 +1675,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1714,10 +1727,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292162</v>
+        <v>131292188</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,31 +1738,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1757,10 +1765,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528917</v>
+        <v>528907</v>
       </c>
       <c r="R10" t="n">
-        <v>7000356</v>
+        <v>7000430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1797,7 +1805,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1806,12 +1814,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1826,12 +1835,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1849,10 +1858,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292254</v>
+        <v>131292273</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,31 +1869,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1892,10 +1896,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529159</v>
+        <v>528941</v>
       </c>
       <c r="R11" t="n">
-        <v>7000453</v>
+        <v>7000481</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1930,17 +1934,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292163</v>
+        <v>131292191</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,31 +2725,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2757,10 +2752,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528921</v>
+        <v>528927</v>
       </c>
       <c r="R18" t="n">
-        <v>7000354</v>
+        <v>7000340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2797,7 +2792,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2806,6 +2801,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2824,14 +2820,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2849,10 +2840,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292191</v>
+        <v>131292265</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>79006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2860,21 +2851,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2887,10 +2878,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528927</v>
+        <v>529126</v>
       </c>
       <c r="R19" t="n">
-        <v>7000340</v>
+        <v>7000447</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2925,11 +2916,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2943,21 +2929,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2975,10 +2946,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292265</v>
+        <v>131292263</v>
       </c>
       <c r="B20" t="n">
-        <v>79006</v>
+        <v>80354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2986,26 +2957,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3013,10 +2988,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529126</v>
+        <v>528966</v>
       </c>
       <c r="R20" t="n">
-        <v>7000447</v>
+        <v>7000477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3051,6 +3026,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3064,6 +3044,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292263</v>
+        <v>131292163</v>
       </c>
       <c r="B21" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,28 +3092,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3123,10 +3124,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528966</v>
+        <v>528921</v>
       </c>
       <c r="R21" t="n">
-        <v>7000477</v>
+        <v>7000354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3163,7 +3164,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3172,7 +3173,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3183,22 +3183,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131292165</v>
+        <v>131292274</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3485,31 +3485,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3517,10 +3512,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528924</v>
+        <v>528983</v>
       </c>
       <c r="R24" t="n">
-        <v>7000345</v>
+        <v>7000463</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3555,17 +3550,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3584,14 +3575,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3609,7 +3595,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131292274</v>
+        <v>131292271</v>
       </c>
       <c r="B25" t="n">
         <v>79249</v>
@@ -3647,10 +3633,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528983</v>
+        <v>529122</v>
       </c>
       <c r="R25" t="n">
-        <v>7000463</v>
+        <v>7000459</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3730,10 +3716,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131292271</v>
+        <v>131292165</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3741,26 +3727,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3768,10 +3759,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529122</v>
+        <v>528924</v>
       </c>
       <c r="R26" t="n">
-        <v>7000459</v>
+        <v>7000345</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3806,13 +3797,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3831,9 +3826,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292249</v>
+        <v>131292157</v>
       </c>
       <c r="B29" t="n">
-        <v>83229</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,26 +4118,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4145,10 +4150,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528960</v>
+        <v>528904</v>
       </c>
       <c r="R29" t="n">
-        <v>7000493</v>
+        <v>7000487</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4183,19 +4188,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4208,9 +4217,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4228,10 +4242,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292160</v>
+        <v>131292249</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>83229</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4239,31 +4253,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4271,10 +4280,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528916</v>
+        <v>528960</v>
       </c>
       <c r="R30" t="n">
-        <v>7000358</v>
+        <v>7000493</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4309,23 +4318,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4338,14 +4343,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292157</v>
+        <v>131292160</v>
       </c>
       <c r="B32" t="n">
         <v>57887</v>
@@ -4531,7 +4531,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528904</v>
+        <v>528916</v>
       </c>
       <c r="R32" t="n">
-        <v>7000487</v>
+        <v>7000358</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292257</v>
+        <v>131292153</v>
       </c>
       <c r="B3" t="n">
         <v>57887</v>
@@ -843,7 +843,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528915</v>
+        <v>528908</v>
       </c>
       <c r="R3" t="n">
-        <v>7000264</v>
+        <v>7000510</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en granstam vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,9 +920,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -940,7 +945,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131292153</v>
+        <v>131292257</v>
       </c>
       <c r="B4" t="n">
         <v>57887</v>
@@ -973,7 +978,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -983,10 +988,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528908</v>
+        <v>528915</v>
       </c>
       <c r="R4" t="n">
-        <v>7000510</v>
+        <v>7000264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en granstam vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,14 +1055,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292162</v>
+        <v>131292254</v>
       </c>
       <c r="B6" t="n">
         <v>57887</v>
@@ -1243,7 +1243,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528917</v>
+        <v>529159</v>
       </c>
       <c r="R6" t="n">
-        <v>7000356</v>
+        <v>7000453</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1320,14 +1320,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1345,7 +1340,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292254</v>
+        <v>131292162</v>
       </c>
       <c r="B7" t="n">
         <v>57887</v>
@@ -1378,7 +1373,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1388,10 +1383,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529159</v>
+        <v>528917</v>
       </c>
       <c r="R7" t="n">
-        <v>7000453</v>
+        <v>7000356</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1428,7 +1423,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,7 +1437,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1455,9 +1450,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292191</v>
+        <v>131292163</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,26 +2725,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2752,10 +2757,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528927</v>
+        <v>528921</v>
       </c>
       <c r="R18" t="n">
-        <v>7000340</v>
+        <v>7000354</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2792,7 +2797,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2801,7 +2806,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2820,9 +2824,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2840,10 +2849,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292265</v>
+        <v>131292191</v>
       </c>
       <c r="B19" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2851,21 +2860,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2878,10 +2887,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529126</v>
+        <v>528927</v>
       </c>
       <c r="R19" t="n">
-        <v>7000447</v>
+        <v>7000340</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2916,6 +2925,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2929,6 +2943,21 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2946,10 +2975,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292263</v>
+        <v>131292265</v>
       </c>
       <c r="B20" t="n">
-        <v>80354</v>
+        <v>79006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,30 +2986,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2988,10 +3013,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528966</v>
+        <v>529126</v>
       </c>
       <c r="R20" t="n">
-        <v>7000477</v>
+        <v>7000447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3026,11 +3051,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3044,26 +3064,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292163</v>
+        <v>131292263</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,29 +3092,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3124,10 +3123,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528921</v>
+        <v>528966</v>
       </c>
       <c r="R21" t="n">
-        <v>7000354</v>
+        <v>7000477</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3164,7 +3163,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3173,6 +3172,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3183,22 +3183,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292157</v>
+        <v>131292249</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>83229</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,31 +4118,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4150,10 +4145,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528904</v>
+        <v>528960</v>
       </c>
       <c r="R29" t="n">
-        <v>7000487</v>
+        <v>7000493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4188,23 +4183,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4217,14 +4208,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4242,10 +4228,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292249</v>
+        <v>131292160</v>
       </c>
       <c r="B30" t="n">
-        <v>83229</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4253,26 +4239,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4280,10 +4271,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528960</v>
+        <v>528916</v>
       </c>
       <c r="R30" t="n">
-        <v>7000493</v>
+        <v>7000358</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4318,19 +4309,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4343,9 +4338,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292160</v>
+        <v>131292157</v>
       </c>
       <c r="B32" t="n">
         <v>57887</v>
@@ -4531,7 +4531,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528916</v>
+        <v>528904</v>
       </c>
       <c r="R32" t="n">
-        <v>7000358</v>
+        <v>7000487</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4894,10 +4894,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131292192</v>
+        <v>131292159</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4905,26 +4905,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4932,10 +4937,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528927</v>
+        <v>528913</v>
       </c>
       <c r="R35" t="n">
-        <v>7000269</v>
+        <v>7000365</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4972,7 +4977,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i tallskog.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4981,13 +4986,12 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5000,9 +5004,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5020,7 +5029,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131292187</v>
+        <v>131292192</v>
       </c>
       <c r="B36" t="n">
         <v>79249</v>
@@ -5058,10 +5067,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528912</v>
+        <v>528927</v>
       </c>
       <c r="R36" t="n">
-        <v>7000471</v>
+        <v>7000269</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5098,7 +5107,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Bland andra hänglavar på gran i tallskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5113,7 +5122,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5146,10 +5155,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131292159</v>
+        <v>131292187</v>
       </c>
       <c r="B37" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5157,31 +5166,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5189,10 +5193,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528913</v>
+        <v>528912</v>
       </c>
       <c r="R37" t="n">
-        <v>7000365</v>
+        <v>7000471</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5229,7 +5233,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5238,6 +5242,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5256,14 +5261,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292161</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292153</v>
+        <v>131292257</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528908</v>
+        <v>528915</v>
       </c>
       <c r="R3" t="n">
-        <v>7000510</v>
+        <v>7000264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en granstam vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,14 +920,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131292257</v>
+        <v>131292153</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +973,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -988,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528915</v>
+        <v>528908</v>
       </c>
       <c r="R4" t="n">
-        <v>7000264</v>
+        <v>7000510</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en granstam vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,9 +1050,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
         <v>131292255</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292254</v>
+        <v>131292182</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,31 +1221,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1253,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529159</v>
+        <v>528964</v>
       </c>
       <c r="R6" t="n">
-        <v>7000453</v>
+        <v>7000504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1293,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,6 +1297,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1340,10 +1336,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292162</v>
+        <v>131292184</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,31 +1347,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1383,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528917</v>
+        <v>528962</v>
       </c>
       <c r="R7" t="n">
-        <v>7000356</v>
+        <v>7000560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1423,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,12 +1423,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1450,14 +1442,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1475,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292182</v>
+        <v>131292188</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,10 +1500,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528964</v>
+        <v>528907</v>
       </c>
       <c r="R8" t="n">
-        <v>7000504</v>
+        <v>7000430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1553,7 +1540,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,9 +1568,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1601,10 +1593,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292184</v>
+        <v>131292273</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1639,10 +1631,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528962</v>
+        <v>528941</v>
       </c>
       <c r="R9" t="n">
-        <v>7000560</v>
+        <v>7000481</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1675,11 +1667,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1727,10 +1714,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292188</v>
+        <v>131292162</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,26 +1725,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1765,10 +1757,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528907</v>
+        <v>528917</v>
       </c>
       <c r="R10" t="n">
-        <v>7000430</v>
+        <v>7000356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1805,7 +1797,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,13 +1806,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1835,12 +1826,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1858,10 +1849,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292273</v>
+        <v>131292254</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,26 +1860,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1896,10 +1892,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528941</v>
+        <v>529159</v>
       </c>
       <c r="R11" t="n">
-        <v>7000481</v>
+        <v>7000453</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1934,13 +1930,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>131292270</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131292183</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131292149</v>
       </c>
       <c r="B14" t="n">
-        <v>56702</v>
+        <v>56703</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>131292186</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>131292181</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>131292185</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292163</v>
+        <v>131292191</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,31 +2725,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2757,10 +2752,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528921</v>
+        <v>528927</v>
       </c>
       <c r="R18" t="n">
-        <v>7000354</v>
+        <v>7000340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2797,7 +2792,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2806,6 +2801,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2824,14 +2820,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2849,10 +2840,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292191</v>
+        <v>131292265</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2860,21 +2851,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2887,10 +2878,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528927</v>
+        <v>529126</v>
       </c>
       <c r="R19" t="n">
-        <v>7000340</v>
+        <v>7000447</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2925,11 +2916,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2943,21 +2929,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2975,10 +2946,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292265</v>
+        <v>131292263</v>
       </c>
       <c r="B20" t="n">
-        <v>79006</v>
+        <v>80355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2986,26 +2957,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3013,10 +2988,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529126</v>
+        <v>528966</v>
       </c>
       <c r="R20" t="n">
-        <v>7000447</v>
+        <v>7000477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3051,6 +3026,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3064,6 +3044,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292263</v>
+        <v>131292163</v>
       </c>
       <c r="B21" t="n">
-        <v>80354</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,28 +3092,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3123,10 +3124,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528966</v>
+        <v>528921</v>
       </c>
       <c r="R21" t="n">
-        <v>7000477</v>
+        <v>7000354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3163,7 +3164,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3172,7 +3173,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3183,22 +3183,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
         <v>131292256</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>131292260</v>
       </c>
       <c r="B23" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>131292274</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>131292271</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>131292165</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131292170</v>
+        <v>131292190</v>
       </c>
       <c r="B27" t="n">
-        <v>80354</v>
+        <v>79250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3862,30 +3862,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3893,10 +3889,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528917</v>
+        <v>528945</v>
       </c>
       <c r="R27" t="n">
-        <v>7000532</v>
+        <v>7000349</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3931,6 +3927,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På flera granar i klenvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3943,27 +3944,22 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3981,10 +3977,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131292190</v>
+        <v>131292170</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>80355</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3992,26 +3988,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528945</v>
+        <v>528917</v>
       </c>
       <c r="R28" t="n">
-        <v>7000349</v>
+        <v>7000532</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4057,11 +4057,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På flera granar i klenvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4074,22 +4069,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292249</v>
+        <v>131292166</v>
       </c>
       <c r="B29" t="n">
-        <v>83229</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,26 +4118,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4145,10 +4150,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528960</v>
+        <v>528920</v>
       </c>
       <c r="R29" t="n">
-        <v>7000493</v>
+        <v>7000269</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4183,19 +4188,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4208,9 +4217,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4231,7 +4245,7 @@
         <v>131292160</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4363,10 +4377,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292166</v>
+        <v>131292157</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4406,10 +4420,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528920</v>
+        <v>528904</v>
       </c>
       <c r="R31" t="n">
-        <v>7000269</v>
+        <v>7000487</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4446,7 +4460,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4460,7 +4474,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4498,10 +4512,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292157</v>
+        <v>131292249</v>
       </c>
       <c r="B32" t="n">
-        <v>57887</v>
+        <v>83230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4509,31 +4523,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4541,10 +4550,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528904</v>
+        <v>528960</v>
       </c>
       <c r="R32" t="n">
-        <v>7000487</v>
+        <v>7000493</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4579,23 +4588,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4608,14 +4613,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4636,7 +4636,7 @@
         <v>131292264</v>
       </c>
       <c r="B33" t="n">
-        <v>78261</v>
+        <v>78262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>131292164</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131292159</v>
+        <v>131292192</v>
       </c>
       <c r="B35" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4905,31 +4905,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4937,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528913</v>
+        <v>528927</v>
       </c>
       <c r="R35" t="n">
-        <v>7000365</v>
+        <v>7000269</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4977,7 +4972,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Bland andra hänglavar på gran i tallskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4986,12 +4981,13 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5004,14 +5000,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5029,10 +5020,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131292192</v>
+        <v>131292187</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5067,10 +5058,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528927</v>
+        <v>528912</v>
       </c>
       <c r="R36" t="n">
-        <v>7000269</v>
+        <v>7000471</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5107,7 +5098,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i tallskog.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5122,7 +5113,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5155,10 +5146,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131292187</v>
+        <v>131292159</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5166,26 +5157,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5193,10 +5189,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528912</v>
+        <v>528913</v>
       </c>
       <c r="R37" t="n">
-        <v>7000471</v>
+        <v>7000365</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5233,7 +5229,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5242,7 +5238,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5261,9 +5256,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5284,7 +5284,7 @@
         <v>131292267</v>
       </c>
       <c r="B38" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>131292189</v>
       </c>
       <c r="B39" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131292161</v>
+        <v>131292153</v>
       </c>
       <c r="B2" t="n">
         <v>57888</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528920</v>
+        <v>528908</v>
       </c>
       <c r="R2" t="n">
-        <v>7000358</v>
+        <v>7000510</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en granstam vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292257</v>
+        <v>131292161</v>
       </c>
       <c r="B3" t="n">
         <v>57888</v>
@@ -843,7 +843,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528915</v>
+        <v>528920</v>
       </c>
       <c r="R3" t="n">
-        <v>7000264</v>
+        <v>7000358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,9 +920,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -940,7 +945,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131292153</v>
+        <v>131292257</v>
       </c>
       <c r="B4" t="n">
         <v>57888</v>
@@ -973,7 +978,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -983,10 +988,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528908</v>
+        <v>528915</v>
       </c>
       <c r="R4" t="n">
-        <v>7000510</v>
+        <v>7000264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en granstam vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,14 +1055,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1336,7 +1336,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292184</v>
+        <v>131292188</v>
       </c>
       <c r="B7" t="n">
         <v>79250</v>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528962</v>
+        <v>528907</v>
       </c>
       <c r="R7" t="n">
-        <v>7000560</v>
+        <v>7000430</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,9 +1442,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292188</v>
+        <v>131292162</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,26 +1478,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1500,10 +1510,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528907</v>
+        <v>528917</v>
       </c>
       <c r="R8" t="n">
-        <v>7000430</v>
+        <v>7000356</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,7 +1550,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1549,13 +1559,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1570,12 +1579,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1593,10 +1602,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292273</v>
+        <v>131292254</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,26 +1613,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1631,10 +1645,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528941</v>
+        <v>529159</v>
       </c>
       <c r="R9" t="n">
-        <v>7000481</v>
+        <v>7000453</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,13 +1683,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1714,10 +1732,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292162</v>
+        <v>131292184</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,31 +1743,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1757,10 +1770,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528917</v>
+        <v>528962</v>
       </c>
       <c r="R10" t="n">
-        <v>7000356</v>
+        <v>7000560</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1797,7 +1810,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1806,12 +1819,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1824,14 +1838,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1849,10 +1858,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292254</v>
+        <v>131292273</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,31 +1869,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1892,10 +1896,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529159</v>
+        <v>528941</v>
       </c>
       <c r="R11" t="n">
-        <v>7000453</v>
+        <v>7000481</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1930,17 +1934,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292191</v>
+        <v>131292163</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,26 +2725,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2752,10 +2757,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528927</v>
+        <v>528921</v>
       </c>
       <c r="R18" t="n">
-        <v>7000340</v>
+        <v>7000354</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2792,7 +2797,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2801,7 +2806,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2820,9 +2824,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2840,10 +2849,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292265</v>
+        <v>131292191</v>
       </c>
       <c r="B19" t="n">
-        <v>79007</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2851,21 +2860,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2878,10 +2887,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529126</v>
+        <v>528927</v>
       </c>
       <c r="R19" t="n">
-        <v>7000447</v>
+        <v>7000340</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2916,6 +2925,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2929,6 +2943,21 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2946,10 +2975,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292263</v>
+        <v>131292265</v>
       </c>
       <c r="B20" t="n">
-        <v>80355</v>
+        <v>79007</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,30 +2986,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2988,10 +3013,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528966</v>
+        <v>529126</v>
       </c>
       <c r="R20" t="n">
-        <v>7000477</v>
+        <v>7000447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3026,11 +3051,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3044,26 +3064,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292163</v>
+        <v>131292263</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>80355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,29 +3092,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3124,10 +3123,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528921</v>
+        <v>528966</v>
       </c>
       <c r="R21" t="n">
-        <v>7000354</v>
+        <v>7000477</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3164,7 +3163,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3173,6 +3172,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3183,22 +3183,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131292256</v>
+        <v>131292260</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>58047</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3227,42 +3227,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528997</v>
+        <v>529105</v>
       </c>
       <c r="R22" t="n">
-        <v>7000374</v>
+        <v>7000513</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3299,7 +3307,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1st födosökande talltita i lämplig häckbiotop.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3316,19 +3324,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3346,10 +3344,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131292260</v>
+        <v>131292256</v>
       </c>
       <c r="B23" t="n">
-        <v>58047</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3357,50 +3355,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529105</v>
+        <v>528997</v>
       </c>
       <c r="R23" t="n">
-        <v>7000513</v>
+        <v>7000374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3437,7 +3427,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1st födosökande talltita i lämplig häckbiotop.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3454,9 +3444,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131292190</v>
+        <v>131292170</v>
       </c>
       <c r="B27" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3862,26 +3862,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3889,10 +3893,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528945</v>
+        <v>528917</v>
       </c>
       <c r="R27" t="n">
-        <v>7000349</v>
+        <v>7000532</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3927,11 +3931,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På flera granar i klenvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3944,22 +3943,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3977,10 +3981,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131292170</v>
+        <v>131292190</v>
       </c>
       <c r="B28" t="n">
-        <v>80355</v>
+        <v>79250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3988,30 +3992,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528917</v>
+        <v>528945</v>
       </c>
       <c r="R28" t="n">
-        <v>7000532</v>
+        <v>7000349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4057,6 +4057,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På flera granar i klenvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4069,27 +4074,22 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292166</v>
+        <v>131292249</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>83230</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,31 +4118,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4150,10 +4145,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528920</v>
+        <v>528960</v>
       </c>
       <c r="R29" t="n">
-        <v>7000269</v>
+        <v>7000493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4188,23 +4183,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4217,14 +4208,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4242,7 +4228,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292160</v>
+        <v>131292166</v>
       </c>
       <c r="B30" t="n">
         <v>57888</v>
@@ -4275,7 +4261,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4285,10 +4271,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528916</v>
+        <v>528920</v>
       </c>
       <c r="R30" t="n">
-        <v>7000358</v>
+        <v>7000269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4325,7 +4311,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4339,7 +4325,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4377,7 +4363,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292157</v>
+        <v>131292160</v>
       </c>
       <c r="B31" t="n">
         <v>57888</v>
@@ -4410,7 +4396,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4420,10 +4406,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528904</v>
+        <v>528916</v>
       </c>
       <c r="R31" t="n">
-        <v>7000487</v>
+        <v>7000358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4460,7 +4446,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4512,10 +4498,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292249</v>
+        <v>131292157</v>
       </c>
       <c r="B32" t="n">
-        <v>83230</v>
+        <v>57888</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4523,26 +4509,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4550,10 +4541,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528960</v>
+        <v>528904</v>
       </c>
       <c r="R32" t="n">
-        <v>7000493</v>
+        <v>7000487</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4588,19 +4579,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4613,9 +4608,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292162</v>
+        <v>131292184</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,31 +1478,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1510,10 +1505,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528917</v>
+        <v>528962</v>
       </c>
       <c r="R8" t="n">
-        <v>7000356</v>
+        <v>7000560</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1550,7 +1545,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1559,12 +1554,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1577,14 +1573,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1602,10 +1593,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292254</v>
+        <v>131292273</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,31 +1604,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1645,10 +1631,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529159</v>
+        <v>528941</v>
       </c>
       <c r="R9" t="n">
-        <v>7000453</v>
+        <v>7000481</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1683,17 +1669,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1732,10 +1714,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292184</v>
+        <v>131292162</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,26 +1725,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1770,10 +1757,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528962</v>
+        <v>528917</v>
       </c>
       <c r="R10" t="n">
-        <v>7000560</v>
+        <v>7000356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1810,7 +1797,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1819,13 +1806,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1838,9 +1824,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1858,10 +1849,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292273</v>
+        <v>131292254</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,26 +1860,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1896,10 +1892,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528941</v>
+        <v>529159</v>
       </c>
       <c r="R11" t="n">
-        <v>7000481</v>
+        <v>7000453</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1934,13 +1930,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292163</v>
+        <v>131292265</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>79007</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,31 +2725,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2757,10 +2752,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528921</v>
+        <v>529126</v>
       </c>
       <c r="R18" t="n">
-        <v>7000354</v>
+        <v>7000447</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2795,43 +2790,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2849,10 +2820,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292191</v>
+        <v>131292263</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2860,26 +2831,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2887,10 +2862,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528927</v>
+        <v>528966</v>
       </c>
       <c r="R19" t="n">
-        <v>7000340</v>
+        <v>7000477</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2927,7 +2902,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2947,17 +2922,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2975,10 +2955,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292265</v>
+        <v>131292163</v>
       </c>
       <c r="B20" t="n">
-        <v>79007</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2986,26 +2966,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3013,10 +2998,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529126</v>
+        <v>528921</v>
       </c>
       <c r="R20" t="n">
-        <v>7000447</v>
+        <v>7000354</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3051,19 +3036,43 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3081,10 +3090,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292263</v>
+        <v>131292191</v>
       </c>
       <c r="B21" t="n">
-        <v>80355</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,30 +3101,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3123,10 +3128,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528966</v>
+        <v>528927</v>
       </c>
       <c r="R21" t="n">
-        <v>7000477</v>
+        <v>7000340</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3163,7 +3168,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3183,22 +3188,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131292260</v>
+        <v>131292256</v>
       </c>
       <c r="B22" t="n">
-        <v>58047</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3227,50 +3227,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529105</v>
+        <v>528997</v>
       </c>
       <c r="R22" t="n">
-        <v>7000513</v>
+        <v>7000374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3307,7 +3299,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1st födosökande talltita i lämplig häckbiotop.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3324,9 +3316,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3344,10 +3346,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131292256</v>
+        <v>131292260</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>58047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3355,42 +3357,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528997</v>
+        <v>529105</v>
       </c>
       <c r="R23" t="n">
-        <v>7000374</v>
+        <v>7000513</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3427,7 +3437,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1st födosökande talltita i lämplig häckbiotop.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3444,19 +3454,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131292153</v>
+        <v>131292161</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528908</v>
+        <v>528920</v>
       </c>
       <c r="R2" t="n">
-        <v>7000510</v>
+        <v>7000358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en granstam vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292161</v>
+        <v>131292257</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528920</v>
+        <v>528915</v>
       </c>
       <c r="R3" t="n">
-        <v>7000358</v>
+        <v>7000264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,14 +920,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131292257</v>
+        <v>131292153</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +973,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -988,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528915</v>
+        <v>528908</v>
       </c>
       <c r="R4" t="n">
-        <v>7000264</v>
+        <v>7000510</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en granstam vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,9 +1050,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
         <v>131292255</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>131292182</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292188</v>
+        <v>131292184</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528907</v>
+        <v>528962</v>
       </c>
       <c r="R7" t="n">
-        <v>7000430</v>
+        <v>7000560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,14 +1442,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292184</v>
+        <v>131292188</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,10 +1500,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528962</v>
+        <v>528907</v>
       </c>
       <c r="R8" t="n">
-        <v>7000560</v>
+        <v>7000430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1545,7 +1540,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,9 +1568,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
         <v>131292273</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>131292162</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>131292254</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>131292270</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131292183</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131292149</v>
       </c>
       <c r="B14" t="n">
-        <v>56703</v>
+        <v>56706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>131292186</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>131292181</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>131292185</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292265</v>
+        <v>131292191</v>
       </c>
       <c r="B18" t="n">
-        <v>79007</v>
+        <v>79253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,21 +2725,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529126</v>
+        <v>528927</v>
       </c>
       <c r="R18" t="n">
-        <v>7000447</v>
+        <v>7000340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2790,6 +2790,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2803,6 +2808,21 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2820,10 +2840,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292263</v>
+        <v>131292265</v>
       </c>
       <c r="B19" t="n">
-        <v>80355</v>
+        <v>79010</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,30 +2851,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2862,10 +2878,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528966</v>
+        <v>529126</v>
       </c>
       <c r="R19" t="n">
-        <v>7000477</v>
+        <v>7000447</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2900,11 +2916,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2918,26 +2929,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2955,10 +2946,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292163</v>
+        <v>131292263</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>80358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2966,29 +2957,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2998,10 +2988,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528921</v>
+        <v>528966</v>
       </c>
       <c r="R20" t="n">
-        <v>7000354</v>
+        <v>7000477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3038,7 +3028,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3047,6 +3037,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3057,22 +3048,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3090,10 +3081,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292191</v>
+        <v>131292163</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3101,26 +3092,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3128,10 +3124,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528927</v>
+        <v>528921</v>
       </c>
       <c r="R21" t="n">
-        <v>7000340</v>
+        <v>7000354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3168,7 +3164,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3177,7 +3173,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3196,9 +3191,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
         <v>131292256</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>131292260</v>
       </c>
       <c r="B23" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131292274</v>
+        <v>131292165</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3485,26 +3485,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3512,10 +3517,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528983</v>
+        <v>528924</v>
       </c>
       <c r="R24" t="n">
-        <v>7000463</v>
+        <v>7000345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3550,13 +3555,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3575,9 +3584,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3595,10 +3609,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131292271</v>
+        <v>131292274</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3633,10 +3647,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529122</v>
+        <v>528983</v>
       </c>
       <c r="R25" t="n">
-        <v>7000459</v>
+        <v>7000463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3716,10 +3730,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131292165</v>
+        <v>131292271</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3727,31 +3741,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3759,10 +3768,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528924</v>
+        <v>529122</v>
       </c>
       <c r="R26" t="n">
-        <v>7000345</v>
+        <v>7000459</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3797,17 +3806,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3826,14 +3831,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131292170</v>
+        <v>131292190</v>
       </c>
       <c r="B27" t="n">
-        <v>80355</v>
+        <v>79253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3862,30 +3862,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3893,10 +3889,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528917</v>
+        <v>528945</v>
       </c>
       <c r="R27" t="n">
-        <v>7000532</v>
+        <v>7000349</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3931,6 +3927,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På flera granar i klenvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3943,27 +3944,22 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3981,10 +3977,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131292190</v>
+        <v>131292170</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>80358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3992,26 +3988,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528945</v>
+        <v>528917</v>
       </c>
       <c r="R28" t="n">
-        <v>7000349</v>
+        <v>7000532</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4057,11 +4057,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På flera granar i klenvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4074,22 +4069,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4110,7 +4110,7 @@
         <v>131292249</v>
       </c>
       <c r="B29" t="n">
-        <v>83230</v>
+        <v>83233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>131292166</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>131292160</v>
       </c>
       <c r="B31" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>131292157</v>
       </c>
       <c r="B32" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>131292264</v>
       </c>
       <c r="B33" t="n">
-        <v>78262</v>
+        <v>78265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>131292164</v>
       </c>
       <c r="B34" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131292192</v>
+        <v>131292187</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528927</v>
+        <v>528912</v>
       </c>
       <c r="R35" t="n">
-        <v>7000269</v>
+        <v>7000471</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i tallskog.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5020,10 +5020,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131292187</v>
+        <v>131292159</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5031,26 +5031,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5058,10 +5063,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528912</v>
+        <v>528913</v>
       </c>
       <c r="R36" t="n">
-        <v>7000471</v>
+        <v>7000365</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5098,7 +5103,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5107,7 +5112,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5126,9 +5130,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5146,10 +5155,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131292159</v>
+        <v>131292192</v>
       </c>
       <c r="B37" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5157,31 +5166,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5189,10 +5193,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528913</v>
+        <v>528927</v>
       </c>
       <c r="R37" t="n">
-        <v>7000365</v>
+        <v>7000269</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5229,7 +5233,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Bland andra hänglavar på gran i tallskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5238,12 +5242,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5256,14 +5261,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5284,7 +5284,7 @@
         <v>131292267</v>
       </c>
       <c r="B38" t="n">
-        <v>91814</v>
+        <v>91817</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>131292189</v>
       </c>
       <c r="B39" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292161</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292257</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131292153</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>131292255</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292182</v>
+        <v>131292162</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,26 +1221,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528964</v>
+        <v>528917</v>
       </c>
       <c r="R6" t="n">
-        <v>7000504</v>
+        <v>7000356</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,7 +1293,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,13 +1302,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1316,9 +1320,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1336,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292184</v>
+        <v>131292182</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,10 +1383,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528962</v>
+        <v>528964</v>
       </c>
       <c r="R7" t="n">
-        <v>7000560</v>
+        <v>7000504</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1423,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1462,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292188</v>
+        <v>131292184</v>
       </c>
       <c r="B8" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,10 +1509,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528907</v>
+        <v>528962</v>
       </c>
       <c r="R8" t="n">
-        <v>7000430</v>
+        <v>7000560</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,7 +1549,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,14 +1577,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1593,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292273</v>
+        <v>131292188</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,10 +1635,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528941</v>
+        <v>528907</v>
       </c>
       <c r="R9" t="n">
-        <v>7000481</v>
+        <v>7000430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,6 +1673,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I god mängd på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1694,9 +1703,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1714,10 +1728,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292162</v>
+        <v>131292273</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,31 +1739,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1757,10 +1766,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528917</v>
+        <v>528941</v>
       </c>
       <c r="R10" t="n">
-        <v>7000356</v>
+        <v>7000481</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1795,23 +1804,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1824,14 +1829,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1852,7 +1852,7 @@
         <v>131292254</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>131292270</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131292183</v>
       </c>
       <c r="B13" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131292149</v>
       </c>
       <c r="B14" t="n">
-        <v>56706</v>
+        <v>56707</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>131292186</v>
       </c>
       <c r="B15" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>131292181</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>131292185</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292191</v>
+        <v>131292265</v>
       </c>
       <c r="B18" t="n">
-        <v>79253</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,21 +2725,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528927</v>
+        <v>529126</v>
       </c>
       <c r="R18" t="n">
-        <v>7000340</v>
+        <v>7000447</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2790,11 +2790,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2808,21 +2803,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2840,10 +2820,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292265</v>
+        <v>131292263</v>
       </c>
       <c r="B19" t="n">
-        <v>79010</v>
+        <v>80359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2851,26 +2831,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2878,10 +2862,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529126</v>
+        <v>528966</v>
       </c>
       <c r="R19" t="n">
-        <v>7000447</v>
+        <v>7000477</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2916,6 +2900,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2929,6 +2918,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2946,10 +2955,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292263</v>
+        <v>131292191</v>
       </c>
       <c r="B20" t="n">
-        <v>80358</v>
+        <v>79254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,30 +2966,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2988,10 +2993,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528966</v>
+        <v>528927</v>
       </c>
       <c r="R20" t="n">
-        <v>7000477</v>
+        <v>7000340</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3028,7 +3033,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3048,22 +3053,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3084,7 +3084,7 @@
         <v>131292163</v>
       </c>
       <c r="B21" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>131292256</v>
       </c>
       <c r="B22" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>131292260</v>
       </c>
       <c r="B23" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131292165</v>
+        <v>131292274</v>
       </c>
       <c r="B24" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3485,31 +3485,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3517,10 +3512,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528924</v>
+        <v>528983</v>
       </c>
       <c r="R24" t="n">
-        <v>7000345</v>
+        <v>7000463</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3555,17 +3550,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3584,14 +3575,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3609,10 +3595,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131292274</v>
+        <v>131292165</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3620,26 +3606,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3647,10 +3638,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528983</v>
+        <v>528924</v>
       </c>
       <c r="R25" t="n">
-        <v>7000463</v>
+        <v>7000345</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3685,13 +3676,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3710,9 +3705,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3733,7 +3733,7 @@
         <v>131292271</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>131292190</v>
       </c>
       <c r="B27" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>131292170</v>
       </c>
       <c r="B28" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>131292249</v>
       </c>
       <c r="B29" t="n">
-        <v>83233</v>
+        <v>83234</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>131292166</v>
       </c>
       <c r="B30" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292160</v>
+        <v>131292264</v>
       </c>
       <c r="B31" t="n">
-        <v>57891</v>
+        <v>78266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4374,31 +4374,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4406,10 +4401,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528916</v>
+        <v>528951</v>
       </c>
       <c r="R31" t="n">
-        <v>7000358</v>
+        <v>7000496</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4444,17 +4439,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4475,12 +4466,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4498,10 +4489,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292157</v>
+        <v>131292160</v>
       </c>
       <c r="B32" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4531,7 +4522,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4541,10 +4532,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528904</v>
+        <v>528916</v>
       </c>
       <c r="R32" t="n">
-        <v>7000487</v>
+        <v>7000358</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4581,7 +4572,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4633,10 +4624,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292264</v>
+        <v>131292157</v>
       </c>
       <c r="B33" t="n">
-        <v>78265</v>
+        <v>57892</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4644,26 +4635,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4671,10 +4667,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528951</v>
+        <v>528904</v>
       </c>
       <c r="R33" t="n">
-        <v>7000496</v>
+        <v>7000487</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4709,13 +4705,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,7 +4762,7 @@
         <v>131292164</v>
       </c>
       <c r="B34" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131292187</v>
+        <v>131292159</v>
       </c>
       <c r="B35" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4905,26 +4905,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4932,10 +4937,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528912</v>
+        <v>528913</v>
       </c>
       <c r="R35" t="n">
-        <v>7000471</v>
+        <v>7000365</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4972,7 +4977,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4981,7 +4986,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5000,9 +5004,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5020,10 +5029,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131292159</v>
+        <v>131292192</v>
       </c>
       <c r="B36" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5031,31 +5040,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5063,10 +5067,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528913</v>
+        <v>528927</v>
       </c>
       <c r="R36" t="n">
-        <v>7000365</v>
+        <v>7000269</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5103,7 +5107,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Bland andra hänglavar på gran i tallskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5112,12 +5116,13 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5130,14 +5135,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5155,10 +5155,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131292192</v>
+        <v>131292187</v>
       </c>
       <c r="B37" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528927</v>
+        <v>528912</v>
       </c>
       <c r="R37" t="n">
-        <v>7000269</v>
+        <v>7000471</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i tallskog.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5284,7 +5284,7 @@
         <v>131292267</v>
       </c>
       <c r="B38" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>131292189</v>
       </c>
       <c r="B39" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292265</v>
+        <v>131292163</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,26 +2725,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2752,10 +2757,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529126</v>
+        <v>528921</v>
       </c>
       <c r="R18" t="n">
-        <v>7000447</v>
+        <v>7000354</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2790,19 +2795,43 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2820,10 +2849,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292263</v>
+        <v>131292191</v>
       </c>
       <c r="B19" t="n">
-        <v>80359</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,30 +2860,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2862,10 +2887,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528966</v>
+        <v>528927</v>
       </c>
       <c r="R19" t="n">
-        <v>7000477</v>
+        <v>7000340</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2902,7 +2927,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2922,22 +2947,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2955,10 +2975,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292191</v>
+        <v>131292265</v>
       </c>
       <c r="B20" t="n">
-        <v>79254</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2966,21 +2986,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2993,10 +3013,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528927</v>
+        <v>529126</v>
       </c>
       <c r="R20" t="n">
-        <v>7000340</v>
+        <v>7000447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3031,11 +3051,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3049,21 +3064,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292163</v>
+        <v>131292263</v>
       </c>
       <c r="B21" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,29 +3092,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3124,10 +3123,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528921</v>
+        <v>528966</v>
       </c>
       <c r="R21" t="n">
-        <v>7000354</v>
+        <v>7000477</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3164,7 +3163,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3173,6 +3172,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3183,22 +3183,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292166</v>
+        <v>131292264</v>
       </c>
       <c r="B30" t="n">
-        <v>57892</v>
+        <v>78266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4239,31 +4239,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4271,10 +4266,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528920</v>
+        <v>528951</v>
       </c>
       <c r="R30" t="n">
-        <v>7000269</v>
+        <v>7000496</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4309,23 +4304,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4340,12 +4331,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4363,10 +4354,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292264</v>
+        <v>131292160</v>
       </c>
       <c r="B31" t="n">
-        <v>78266</v>
+        <v>57892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4374,26 +4365,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4401,10 +4397,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528951</v>
+        <v>528916</v>
       </c>
       <c r="R31" t="n">
-        <v>7000496</v>
+        <v>7000358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4439,13 +4435,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4489,7 +4489,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292160</v>
+        <v>131292157</v>
       </c>
       <c r="B32" t="n">
         <v>57892</v>
@@ -4522,7 +4522,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528916</v>
+        <v>528904</v>
       </c>
       <c r="R32" t="n">
-        <v>7000358</v>
+        <v>7000487</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4624,7 +4624,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292157</v>
+        <v>131292166</v>
       </c>
       <c r="B33" t="n">
         <v>57892</v>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528904</v>
+        <v>528920</v>
       </c>
       <c r="R33" t="n">
-        <v>7000487</v>
+        <v>7000269</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292161</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292257</v>
       </c>
       <c r="B3" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131292153</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>131292255</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>131292162</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292182</v>
+        <v>131292254</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,26 +1356,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1383,10 +1388,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528964</v>
+        <v>529159</v>
       </c>
       <c r="R7" t="n">
-        <v>7000504</v>
+        <v>7000453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1423,7 +1428,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,7 +1437,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1471,10 +1475,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292184</v>
+        <v>131292182</v>
       </c>
       <c r="B8" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528962</v>
+        <v>528964</v>
       </c>
       <c r="R8" t="n">
-        <v>7000560</v>
+        <v>7000504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1549,7 +1553,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1597,10 +1601,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292188</v>
+        <v>131292184</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528907</v>
+        <v>528962</v>
       </c>
       <c r="R9" t="n">
-        <v>7000430</v>
+        <v>7000560</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1675,7 +1679,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,14 +1707,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1728,10 +1727,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292273</v>
+        <v>131292188</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,10 +1765,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528941</v>
+        <v>528907</v>
       </c>
       <c r="R10" t="n">
-        <v>7000481</v>
+        <v>7000430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,6 +1803,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I god mängd på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1829,9 +1833,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1849,10 +1858,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292254</v>
+        <v>131292273</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,31 +1869,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1892,10 +1896,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529159</v>
+        <v>528941</v>
       </c>
       <c r="R11" t="n">
-        <v>7000453</v>
+        <v>7000481</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1930,17 +1934,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>131292270</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131292183</v>
       </c>
       <c r="B13" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131292149</v>
       </c>
       <c r="B14" t="n">
-        <v>56707</v>
+        <v>56712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>131292186</v>
       </c>
       <c r="B15" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>131292181</v>
       </c>
       <c r="B16" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>131292185</v>
       </c>
       <c r="B17" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>131292163</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>131292191</v>
       </c>
       <c r="B19" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>131292265</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79017</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>131292263</v>
       </c>
       <c r="B21" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131292256</v>
+        <v>131292260</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>58057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3227,42 +3227,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528997</v>
+        <v>529105</v>
       </c>
       <c r="R22" t="n">
-        <v>7000374</v>
+        <v>7000513</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3299,7 +3307,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1st födosökande talltita i lämplig häckbiotop.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3316,19 +3324,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3346,10 +3344,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131292260</v>
+        <v>131292256</v>
       </c>
       <c r="B23" t="n">
-        <v>58051</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3357,50 +3355,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529105</v>
+        <v>528997</v>
       </c>
       <c r="R23" t="n">
-        <v>7000513</v>
+        <v>7000374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3437,7 +3427,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1st födosökande talltita i lämplig häckbiotop.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3454,9 +3444,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3477,7 +3477,7 @@
         <v>131292274</v>
       </c>
       <c r="B24" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3595,10 +3595,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131292165</v>
+        <v>131292271</v>
       </c>
       <c r="B25" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3606,31 +3606,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3638,10 +3633,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528924</v>
+        <v>529122</v>
       </c>
       <c r="R25" t="n">
-        <v>7000345</v>
+        <v>7000459</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3676,17 +3671,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3705,14 +3696,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3730,10 +3716,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131292271</v>
+        <v>131292165</v>
       </c>
       <c r="B26" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3741,26 +3727,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3768,10 +3759,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529122</v>
+        <v>528924</v>
       </c>
       <c r="R26" t="n">
-        <v>7000459</v>
+        <v>7000345</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3806,13 +3797,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3831,9 +3826,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131292190</v>
+        <v>131292170</v>
       </c>
       <c r="B27" t="n">
-        <v>79254</v>
+        <v>80365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3862,26 +3862,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3889,10 +3893,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528945</v>
+        <v>528917</v>
       </c>
       <c r="R27" t="n">
-        <v>7000349</v>
+        <v>7000532</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3927,11 +3931,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På flera granar i klenvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3944,22 +3943,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3977,10 +3981,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131292170</v>
+        <v>131292190</v>
       </c>
       <c r="B28" t="n">
-        <v>80359</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3988,30 +3992,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528917</v>
+        <v>528945</v>
       </c>
       <c r="R28" t="n">
-        <v>7000532</v>
+        <v>7000349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4057,6 +4057,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På flera granar i klenvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4069,27 +4074,22 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292249</v>
+        <v>131292166</v>
       </c>
       <c r="B29" t="n">
-        <v>83234</v>
+        <v>57898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,26 +4118,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4145,10 +4150,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528960</v>
+        <v>528920</v>
       </c>
       <c r="R29" t="n">
-        <v>7000493</v>
+        <v>7000269</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4183,19 +4188,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4208,9 +4217,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4228,10 +4242,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292264</v>
+        <v>131292160</v>
       </c>
       <c r="B30" t="n">
-        <v>78266</v>
+        <v>57898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4239,26 +4253,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4266,10 +4285,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528951</v>
+        <v>528916</v>
       </c>
       <c r="R30" t="n">
-        <v>7000496</v>
+        <v>7000358</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4304,13 +4323,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4331,12 +4354,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4354,10 +4377,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292160</v>
+        <v>131292157</v>
       </c>
       <c r="B31" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4387,7 +4410,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4397,10 +4420,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528916</v>
+        <v>528904</v>
       </c>
       <c r="R31" t="n">
-        <v>7000358</v>
+        <v>7000487</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4437,7 +4460,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4489,10 +4512,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292157</v>
+        <v>131292264</v>
       </c>
       <c r="B32" t="n">
-        <v>57892</v>
+        <v>78272</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4500,31 +4523,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4532,10 +4550,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528904</v>
+        <v>528951</v>
       </c>
       <c r="R32" t="n">
-        <v>7000487</v>
+        <v>7000496</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4570,17 +4588,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4601,12 +4615,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4624,10 +4638,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292166</v>
+        <v>131292249</v>
       </c>
       <c r="B33" t="n">
-        <v>57892</v>
+        <v>83240</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4635,31 +4649,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4667,10 +4676,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528920</v>
+        <v>528960</v>
       </c>
       <c r="R33" t="n">
-        <v>7000269</v>
+        <v>7000493</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4705,23 +4714,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4734,14 +4739,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,7 +4762,7 @@
         <v>131292164</v>
       </c>
       <c r="B34" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131292159</v>
+        <v>131292192</v>
       </c>
       <c r="B35" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4905,31 +4905,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4937,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528913</v>
+        <v>528927</v>
       </c>
       <c r="R35" t="n">
-        <v>7000365</v>
+        <v>7000269</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4977,7 +4972,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Bland andra hänglavar på gran i tallskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4986,12 +4981,13 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5004,14 +5000,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5029,10 +5020,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131292192</v>
+        <v>131292187</v>
       </c>
       <c r="B36" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5067,10 +5058,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528927</v>
+        <v>528912</v>
       </c>
       <c r="R36" t="n">
-        <v>7000269</v>
+        <v>7000471</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5107,7 +5098,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i tallskog.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5122,7 +5113,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5155,10 +5146,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131292187</v>
+        <v>131292159</v>
       </c>
       <c r="B37" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5166,26 +5157,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5193,10 +5189,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528912</v>
+        <v>528913</v>
       </c>
       <c r="R37" t="n">
-        <v>7000471</v>
+        <v>7000365</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5233,7 +5229,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5242,7 +5238,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5261,9 +5256,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5284,7 +5284,7 @@
         <v>131292267</v>
       </c>
       <c r="B38" t="n">
-        <v>91818</v>
+        <v>91824</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>131292189</v>
       </c>
       <c r="B39" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292162</v>
+        <v>131292182</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,31 +1221,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1253,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528917</v>
+        <v>528964</v>
       </c>
       <c r="R6" t="n">
-        <v>7000356</v>
+        <v>7000504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1293,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,12 +1297,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1320,14 +1316,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1345,10 +1336,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292254</v>
+        <v>131292184</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,31 +1347,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1388,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529159</v>
+        <v>528962</v>
       </c>
       <c r="R7" t="n">
-        <v>7000453</v>
+        <v>7000560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1428,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,6 +1423,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1475,7 +1462,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292182</v>
+        <v>131292188</v>
       </c>
       <c r="B8" t="n">
         <v>79260</v>
@@ -1513,10 +1500,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528964</v>
+        <v>528907</v>
       </c>
       <c r="R8" t="n">
-        <v>7000504</v>
+        <v>7000430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1553,7 +1540,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,9 +1568,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1601,7 +1593,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292184</v>
+        <v>131292273</v>
       </c>
       <c r="B9" t="n">
         <v>79260</v>
@@ -1639,10 +1631,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528962</v>
+        <v>528941</v>
       </c>
       <c r="R9" t="n">
-        <v>7000560</v>
+        <v>7000481</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1675,11 +1667,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1727,10 +1714,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292188</v>
+        <v>131292162</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,26 +1725,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1765,10 +1757,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528907</v>
+        <v>528917</v>
       </c>
       <c r="R10" t="n">
-        <v>7000430</v>
+        <v>7000356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1805,7 +1797,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,13 +1806,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1835,12 +1826,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1858,10 +1849,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292273</v>
+        <v>131292254</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,26 +1860,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1896,10 +1892,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528941</v>
+        <v>529159</v>
       </c>
       <c r="R11" t="n">
-        <v>7000481</v>
+        <v>7000453</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1934,13 +1930,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292163</v>
+        <v>131292263</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,29 +2725,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2757,10 +2756,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528921</v>
+        <v>528966</v>
       </c>
       <c r="R18" t="n">
-        <v>7000354</v>
+        <v>7000477</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2797,7 +2796,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2806,6 +2805,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2816,22 +2816,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292263</v>
+        <v>131292163</v>
       </c>
       <c r="B21" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,28 +3092,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3123,10 +3124,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528966</v>
+        <v>528921</v>
       </c>
       <c r="R21" t="n">
-        <v>7000477</v>
+        <v>7000354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3163,7 +3164,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3172,7 +3173,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3183,22 +3183,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292166</v>
+        <v>131292249</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>83240</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,31 +4118,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4150,10 +4145,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528920</v>
+        <v>528960</v>
       </c>
       <c r="R29" t="n">
-        <v>7000269</v>
+        <v>7000493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4188,23 +4183,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4217,14 +4208,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4242,7 +4228,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292160</v>
+        <v>131292166</v>
       </c>
       <c r="B30" t="n">
         <v>57898</v>
@@ -4275,7 +4261,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4285,10 +4271,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528916</v>
+        <v>528920</v>
       </c>
       <c r="R30" t="n">
-        <v>7000358</v>
+        <v>7000269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4325,7 +4311,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4339,7 +4325,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4377,7 +4363,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292157</v>
+        <v>131292160</v>
       </c>
       <c r="B31" t="n">
         <v>57898</v>
@@ -4410,7 +4396,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4420,10 +4406,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528904</v>
+        <v>528916</v>
       </c>
       <c r="R31" t="n">
-        <v>7000487</v>
+        <v>7000358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4460,7 +4446,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4512,10 +4498,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292264</v>
+        <v>131292157</v>
       </c>
       <c r="B32" t="n">
-        <v>78272</v>
+        <v>57898</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4523,26 +4509,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4550,10 +4541,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528951</v>
+        <v>528904</v>
       </c>
       <c r="R32" t="n">
-        <v>7000496</v>
+        <v>7000487</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4588,13 +4579,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4615,12 +4610,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292249</v>
+        <v>131292264</v>
       </c>
       <c r="B33" t="n">
-        <v>83240</v>
+        <v>78272</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4649,21 +4644,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4676,10 +4671,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528960</v>
+        <v>528951</v>
       </c>
       <c r="R33" t="n">
-        <v>7000493</v>
+        <v>7000496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4726,7 +4721,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4739,9 +4734,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -2849,10 +2849,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292191</v>
+        <v>131292163</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2860,26 +2860,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528927</v>
+        <v>528921</v>
       </c>
       <c r="R19" t="n">
-        <v>7000340</v>
+        <v>7000354</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2927,7 +2932,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2936,7 +2941,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2955,9 +2959,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2975,10 +2984,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292265</v>
+        <v>131292191</v>
       </c>
       <c r="B20" t="n">
-        <v>79017</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2986,21 +2995,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3013,10 +3022,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529126</v>
+        <v>528927</v>
       </c>
       <c r="R20" t="n">
-        <v>7000447</v>
+        <v>7000340</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3051,6 +3060,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3064,6 +3078,21 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3081,10 +3110,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292163</v>
+        <v>131292265</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>79017</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,31 +3121,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3124,10 +3148,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528921</v>
+        <v>529126</v>
       </c>
       <c r="R21" t="n">
-        <v>7000354</v>
+        <v>7000447</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3162,43 +3186,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -1210,7 +1210,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292182</v>
+        <v>131292184</v>
       </c>
       <c r="B6" t="n">
         <v>79260</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528964</v>
+        <v>528962</v>
       </c>
       <c r="R6" t="n">
-        <v>7000504</v>
+        <v>7000560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1336,7 +1336,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292184</v>
+        <v>131292188</v>
       </c>
       <c r="B7" t="n">
         <v>79260</v>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528962</v>
+        <v>528907</v>
       </c>
       <c r="R7" t="n">
-        <v>7000560</v>
+        <v>7000430</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,9 +1442,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,7 +1467,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292188</v>
+        <v>131292182</v>
       </c>
       <c r="B8" t="n">
         <v>79260</v>
@@ -1500,10 +1505,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528907</v>
+        <v>528964</v>
       </c>
       <c r="R8" t="n">
-        <v>7000430</v>
+        <v>7000504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,7 +1545,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,14 +1573,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131292186</v>
+        <v>131292185</v>
       </c>
       <c r="B15" t="n">
         <v>79260</v>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528927</v>
+        <v>528965</v>
       </c>
       <c r="R15" t="n">
-        <v>7000496</v>
+        <v>7000595</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2415,11 +2415,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2467,7 +2462,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131292181</v>
+        <v>131292186</v>
       </c>
       <c r="B16" t="n">
         <v>79260</v>
@@ -2505,10 +2500,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528974</v>
+        <v>528927</v>
       </c>
       <c r="R16" t="n">
-        <v>7000525</v>
+        <v>7000496</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2545,7 +2540,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Särskilt rikligt med garnlav på en gammal gran.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2593,7 +2588,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131292185</v>
+        <v>131292181</v>
       </c>
       <c r="B17" t="n">
         <v>79260</v>
@@ -2631,10 +2626,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528965</v>
+        <v>528974</v>
       </c>
       <c r="R17" t="n">
-        <v>7000595</v>
+        <v>7000525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2667,6 +2662,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Särskilt rikligt med garnlav på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292263</v>
+        <v>131292163</v>
       </c>
       <c r="B18" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,28 +2725,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2756,10 +2757,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528966</v>
+        <v>528921</v>
       </c>
       <c r="R18" t="n">
-        <v>7000477</v>
+        <v>7000354</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2796,7 +2797,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,7 +2806,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2816,22 +2816,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292163</v>
+        <v>131292191</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2860,31 +2860,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528921</v>
+        <v>528927</v>
       </c>
       <c r="R19" t="n">
-        <v>7000354</v>
+        <v>7000340</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2932,7 +2927,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2941,6 +2936,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2959,14 +2955,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2984,10 +2975,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292191</v>
+        <v>131292265</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79017</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2995,21 +2986,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3022,10 +3013,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528927</v>
+        <v>529126</v>
       </c>
       <c r="R20" t="n">
-        <v>7000340</v>
+        <v>7000447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3060,11 +3051,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3078,21 +3064,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3110,10 +3081,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292265</v>
+        <v>131292263</v>
       </c>
       <c r="B21" t="n">
-        <v>79017</v>
+        <v>80365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3121,26 +3092,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3148,10 +3123,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529126</v>
+        <v>528966</v>
       </c>
       <c r="R21" t="n">
-        <v>7000447</v>
+        <v>7000477</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3186,6 +3161,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3199,6 +3179,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131292260</v>
+        <v>131292256</v>
       </c>
       <c r="B22" t="n">
-        <v>58057</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3227,50 +3227,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529105</v>
+        <v>528997</v>
       </c>
       <c r="R22" t="n">
-        <v>7000513</v>
+        <v>7000374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3307,7 +3299,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1st födosökande talltita i lämplig häckbiotop.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3324,9 +3316,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3344,10 +3346,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131292256</v>
+        <v>131292260</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>58057</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3355,42 +3357,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528997</v>
+        <v>529105</v>
       </c>
       <c r="R23" t="n">
-        <v>7000374</v>
+        <v>7000513</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3427,7 +3437,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1st födosökande talltita i lämplig häckbiotop.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3444,19 +3454,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131292170</v>
+        <v>131292190</v>
       </c>
       <c r="B27" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3862,30 +3862,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3893,10 +3889,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528917</v>
+        <v>528945</v>
       </c>
       <c r="R27" t="n">
-        <v>7000532</v>
+        <v>7000349</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3931,6 +3927,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På flera granar i klenvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3943,27 +3944,22 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3981,10 +3977,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131292190</v>
+        <v>131292170</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3992,26 +3988,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528945</v>
+        <v>528917</v>
       </c>
       <c r="R28" t="n">
-        <v>7000349</v>
+        <v>7000532</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4057,11 +4057,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På flera granar i klenvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4074,22 +4069,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292249</v>
+        <v>131292264</v>
       </c>
       <c r="B29" t="n">
-        <v>83240</v>
+        <v>78272</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,21 +4118,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528960</v>
+        <v>528951</v>
       </c>
       <c r="R29" t="n">
-        <v>7000493</v>
+        <v>7000496</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4208,9 +4208,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4228,10 +4233,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292166</v>
+        <v>131292249</v>
       </c>
       <c r="B30" t="n">
-        <v>57898</v>
+        <v>83240</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4239,31 +4244,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528920</v>
+        <v>528960</v>
       </c>
       <c r="R30" t="n">
-        <v>7000269</v>
+        <v>7000493</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4309,23 +4309,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4338,14 +4334,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4363,7 +4354,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292160</v>
+        <v>131292166</v>
       </c>
       <c r="B31" t="n">
         <v>57898</v>
@@ -4396,7 +4387,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4406,10 +4397,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528916</v>
+        <v>528920</v>
       </c>
       <c r="R31" t="n">
-        <v>7000358</v>
+        <v>7000269</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4446,7 +4437,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4460,7 +4451,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4498,7 +4489,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292157</v>
+        <v>131292160</v>
       </c>
       <c r="B32" t="n">
         <v>57898</v>
@@ -4531,7 +4522,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4541,10 +4532,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528904</v>
+        <v>528916</v>
       </c>
       <c r="R32" t="n">
-        <v>7000487</v>
+        <v>7000358</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4581,7 +4572,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4633,10 +4624,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292264</v>
+        <v>131292157</v>
       </c>
       <c r="B33" t="n">
-        <v>78272</v>
+        <v>57898</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4644,26 +4635,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4671,10 +4667,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528951</v>
+        <v>528904</v>
       </c>
       <c r="R33" t="n">
-        <v>7000496</v>
+        <v>7000487</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4709,13 +4705,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4894,7 +4894,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131292192</v>
+        <v>131292187</v>
       </c>
       <c r="B35" t="n">
         <v>79260</v>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528927</v>
+        <v>528912</v>
       </c>
       <c r="R35" t="n">
-        <v>7000269</v>
+        <v>7000471</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i tallskog.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5020,10 +5020,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131292187</v>
+        <v>131292159</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5031,26 +5031,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5058,10 +5063,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528912</v>
+        <v>528913</v>
       </c>
       <c r="R36" t="n">
-        <v>7000471</v>
+        <v>7000365</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5098,7 +5103,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5107,7 +5112,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5126,9 +5130,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5146,10 +5155,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131292159</v>
+        <v>131292192</v>
       </c>
       <c r="B37" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5157,31 +5166,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5189,10 +5193,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528913</v>
+        <v>528927</v>
       </c>
       <c r="R37" t="n">
-        <v>7000365</v>
+        <v>7000269</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5229,7 +5233,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Bland andra hänglavar på gran i tallskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5238,12 +5242,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5256,14 +5261,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292161</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292257</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131292153</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>131292255</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292184</v>
+        <v>131292182</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528962</v>
+        <v>528964</v>
       </c>
       <c r="R6" t="n">
-        <v>7000560</v>
+        <v>7000504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1336,10 +1336,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292188</v>
+        <v>131292184</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528907</v>
+        <v>528962</v>
       </c>
       <c r="R7" t="n">
-        <v>7000430</v>
+        <v>7000560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,14 +1442,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292182</v>
+        <v>131292188</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,10 +1500,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528964</v>
+        <v>528907</v>
       </c>
       <c r="R8" t="n">
-        <v>7000504</v>
+        <v>7000430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1545,7 +1540,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,9 +1568,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292273</v>
+        <v>131292162</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,26 +1604,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1631,10 +1636,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528941</v>
+        <v>528917</v>
       </c>
       <c r="R9" t="n">
-        <v>7000481</v>
+        <v>7000356</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,19 +1674,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1694,9 +1703,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1714,10 +1728,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292162</v>
+        <v>131292254</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1761,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1757,10 +1771,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528917</v>
+        <v>529159</v>
       </c>
       <c r="R10" t="n">
-        <v>7000356</v>
+        <v>7000453</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1797,7 +1811,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1811,7 +1825,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1824,14 +1838,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1849,10 +1858,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292254</v>
+        <v>131292273</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,31 +1869,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1892,10 +1896,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529159</v>
+        <v>528941</v>
       </c>
       <c r="R11" t="n">
-        <v>7000453</v>
+        <v>7000481</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1930,17 +1934,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>131292270</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131292183</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131292149</v>
       </c>
       <c r="B14" t="n">
-        <v>56712</v>
+        <v>56713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131292185</v>
+        <v>131292186</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528965</v>
+        <v>528927</v>
       </c>
       <c r="R15" t="n">
-        <v>7000595</v>
+        <v>7000496</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2415,6 +2415,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2462,10 +2467,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131292186</v>
+        <v>131292181</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2500,10 +2505,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528927</v>
+        <v>528974</v>
       </c>
       <c r="R16" t="n">
-        <v>7000496</v>
+        <v>7000525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2540,7 +2545,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Särskilt rikligt med garnlav på en gammal gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2588,10 +2593,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131292181</v>
+        <v>131292185</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,10 +2631,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528974</v>
+        <v>528965</v>
       </c>
       <c r="R17" t="n">
-        <v>7000525</v>
+        <v>7000595</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2662,11 +2667,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Särskilt rikligt med garnlav på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2717,7 +2717,7 @@
         <v>131292163</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>131292191</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>131292265</v>
       </c>
       <c r="B20" t="n">
-        <v>79017</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>131292263</v>
       </c>
       <c r="B21" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131292256</v>
+        <v>131292260</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>58058</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3227,42 +3227,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528997</v>
+        <v>529105</v>
       </c>
       <c r="R22" t="n">
-        <v>7000374</v>
+        <v>7000513</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3299,7 +3307,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1st födosökande talltita i lämplig häckbiotop.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3316,19 +3324,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3346,10 +3344,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131292260</v>
+        <v>131292256</v>
       </c>
       <c r="B23" t="n">
-        <v>58057</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3357,50 +3355,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529105</v>
+        <v>528997</v>
       </c>
       <c r="R23" t="n">
-        <v>7000513</v>
+        <v>7000374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3437,7 +3427,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1st födosökande talltita i lämplig häckbiotop.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3454,9 +3444,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3477,7 +3477,7 @@
         <v>131292274</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>131292271</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>131292165</v>
       </c>
       <c r="B26" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131292190</v>
+        <v>131292170</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>80366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3862,26 +3862,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3889,10 +3893,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528945</v>
+        <v>528917</v>
       </c>
       <c r="R27" t="n">
-        <v>7000349</v>
+        <v>7000532</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3927,11 +3931,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På flera granar i klenvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3944,22 +3943,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3977,10 +3981,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131292170</v>
+        <v>131292190</v>
       </c>
       <c r="B28" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3988,30 +3992,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528917</v>
+        <v>528945</v>
       </c>
       <c r="R28" t="n">
-        <v>7000532</v>
+        <v>7000349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4057,6 +4057,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På flera granar i klenvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4069,27 +4074,22 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292264</v>
+        <v>131292166</v>
       </c>
       <c r="B29" t="n">
-        <v>78272</v>
+        <v>57899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,26 +4118,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4145,10 +4150,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528951</v>
+        <v>528920</v>
       </c>
       <c r="R29" t="n">
-        <v>7000496</v>
+        <v>7000269</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4183,19 +4188,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4210,12 +4219,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4233,10 +4242,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292249</v>
+        <v>131292160</v>
       </c>
       <c r="B30" t="n">
-        <v>83240</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4244,26 +4253,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4271,10 +4285,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528960</v>
+        <v>528916</v>
       </c>
       <c r="R30" t="n">
-        <v>7000493</v>
+        <v>7000358</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4309,19 +4323,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4334,9 +4352,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4354,10 +4377,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292166</v>
+        <v>131292157</v>
       </c>
       <c r="B31" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4397,10 +4420,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528920</v>
+        <v>528904</v>
       </c>
       <c r="R31" t="n">
-        <v>7000269</v>
+        <v>7000487</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4437,7 +4460,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4451,7 +4474,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4489,10 +4512,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292160</v>
+        <v>131292264</v>
       </c>
       <c r="B32" t="n">
-        <v>57898</v>
+        <v>78273</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4500,31 +4523,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4532,10 +4550,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528916</v>
+        <v>528951</v>
       </c>
       <c r="R32" t="n">
-        <v>7000358</v>
+        <v>7000496</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4570,17 +4588,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4601,12 +4615,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4624,10 +4638,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292157</v>
+        <v>131292249</v>
       </c>
       <c r="B33" t="n">
-        <v>57898</v>
+        <v>83241</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4635,31 +4649,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4667,10 +4676,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528904</v>
+        <v>528960</v>
       </c>
       <c r="R33" t="n">
-        <v>7000487</v>
+        <v>7000493</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4705,23 +4714,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4734,14 +4739,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,7 +4762,7 @@
         <v>131292164</v>
       </c>
       <c r="B34" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131292187</v>
+        <v>131292192</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528912</v>
+        <v>528927</v>
       </c>
       <c r="R35" t="n">
-        <v>7000471</v>
+        <v>7000269</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Bland andra hänglavar på gran i tallskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5020,10 +5020,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131292159</v>
+        <v>131292187</v>
       </c>
       <c r="B36" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5031,31 +5031,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5063,10 +5058,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528913</v>
+        <v>528912</v>
       </c>
       <c r="R36" t="n">
-        <v>7000365</v>
+        <v>7000471</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5103,7 +5098,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5112,6 +5107,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5130,14 +5126,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5155,10 +5146,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131292192</v>
+        <v>131292159</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5166,26 +5157,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5193,10 +5189,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528927</v>
+        <v>528913</v>
       </c>
       <c r="R37" t="n">
-        <v>7000269</v>
+        <v>7000365</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5233,7 +5229,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i tallskog.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5242,13 +5238,12 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5261,9 +5256,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5284,7 +5284,7 @@
         <v>131292267</v>
       </c>
       <c r="B38" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>131292189</v>
       </c>
       <c r="B39" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292161</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292257</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131292153</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>131292255</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292182</v>
+        <v>131292162</v>
       </c>
       <c r="B6" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,26 +1221,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528964</v>
+        <v>528917</v>
       </c>
       <c r="R6" t="n">
-        <v>7000504</v>
+        <v>7000356</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,7 +1293,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,13 +1302,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1316,9 +1320,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1336,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292184</v>
+        <v>131292254</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,26 +1356,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1374,10 +1388,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528962</v>
+        <v>529159</v>
       </c>
       <c r="R7" t="n">
-        <v>7000560</v>
+        <v>7000453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1428,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,7 +1437,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1462,10 +1475,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292188</v>
+        <v>131292182</v>
       </c>
       <c r="B8" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528907</v>
+        <v>528964</v>
       </c>
       <c r="R8" t="n">
-        <v>7000430</v>
+        <v>7000504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,7 +1553,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,14 +1581,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1593,10 +1601,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292162</v>
+        <v>131292184</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,31 +1612,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1636,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528917</v>
+        <v>528962</v>
       </c>
       <c r="R9" t="n">
-        <v>7000356</v>
+        <v>7000560</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1676,7 +1679,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1685,12 +1688,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1703,14 +1707,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1728,10 +1727,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292254</v>
+        <v>131292188</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,31 +1738,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1771,10 +1765,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529159</v>
+        <v>528907</v>
       </c>
       <c r="R10" t="n">
-        <v>7000453</v>
+        <v>7000430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1811,7 +1805,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,6 +1814,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1838,9 +1833,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1861,7 +1861,7 @@
         <v>131292273</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>131292270</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131292183</v>
       </c>
       <c r="B13" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131292149</v>
       </c>
       <c r="B14" t="n">
-        <v>56713</v>
+        <v>56716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>131292186</v>
       </c>
       <c r="B15" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>131292181</v>
       </c>
       <c r="B16" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>131292185</v>
       </c>
       <c r="B17" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>131292163</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>131292191</v>
       </c>
       <c r="B19" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>131292265</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>131292263</v>
       </c>
       <c r="B21" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131292260</v>
+        <v>131292256</v>
       </c>
       <c r="B22" t="n">
-        <v>58058</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3227,50 +3227,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529105</v>
+        <v>528997</v>
       </c>
       <c r="R22" t="n">
-        <v>7000513</v>
+        <v>7000374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3307,7 +3299,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1st födosökande talltita i lämplig häckbiotop.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3324,9 +3316,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3344,10 +3346,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131292256</v>
+        <v>131292260</v>
       </c>
       <c r="B23" t="n">
-        <v>57899</v>
+        <v>58061</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3355,42 +3357,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528997</v>
+        <v>529105</v>
       </c>
       <c r="R23" t="n">
-        <v>7000374</v>
+        <v>7000513</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3427,7 +3437,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1st födosökande talltita i lämplig häckbiotop.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3444,19 +3454,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad skog men inslag av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3477,7 +3477,7 @@
         <v>131292274</v>
       </c>
       <c r="B24" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3595,10 +3595,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131292271</v>
+        <v>131292165</v>
       </c>
       <c r="B25" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3606,26 +3606,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3633,10 +3638,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529122</v>
+        <v>528924</v>
       </c>
       <c r="R25" t="n">
-        <v>7000459</v>
+        <v>7000345</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3671,13 +3676,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3696,9 +3705,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3716,10 +3730,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131292165</v>
+        <v>131292271</v>
       </c>
       <c r="B26" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3727,31 +3741,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3759,10 +3768,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528924</v>
+        <v>529122</v>
       </c>
       <c r="R26" t="n">
-        <v>7000345</v>
+        <v>7000459</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3797,17 +3806,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3826,14 +3831,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3854,7 +3854,7 @@
         <v>131292170</v>
       </c>
       <c r="B27" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>131292190</v>
       </c>
       <c r="B28" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292166</v>
+        <v>131292249</v>
       </c>
       <c r="B29" t="n">
-        <v>57899</v>
+        <v>83244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,31 +4118,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4150,10 +4145,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528920</v>
+        <v>528960</v>
       </c>
       <c r="R29" t="n">
-        <v>7000269</v>
+        <v>7000493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4188,23 +4183,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4217,14 +4208,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4242,10 +4228,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292160</v>
+        <v>131292166</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4275,7 +4261,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4285,10 +4271,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528916</v>
+        <v>528920</v>
       </c>
       <c r="R30" t="n">
-        <v>7000358</v>
+        <v>7000269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4325,7 +4311,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4339,7 +4325,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4377,10 +4363,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292157</v>
+        <v>131292160</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4410,7 +4396,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4420,10 +4406,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528904</v>
+        <v>528916</v>
       </c>
       <c r="R31" t="n">
-        <v>7000487</v>
+        <v>7000358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4460,7 +4446,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4512,10 +4498,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292264</v>
+        <v>131292157</v>
       </c>
       <c r="B32" t="n">
-        <v>78273</v>
+        <v>57902</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4523,26 +4509,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4550,10 +4541,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528951</v>
+        <v>528904</v>
       </c>
       <c r="R32" t="n">
-        <v>7000496</v>
+        <v>7000487</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4588,13 +4579,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4615,12 +4610,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292249</v>
+        <v>131292264</v>
       </c>
       <c r="B33" t="n">
-        <v>83241</v>
+        <v>78276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4649,21 +4644,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4676,10 +4671,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528960</v>
+        <v>528951</v>
       </c>
       <c r="R33" t="n">
-        <v>7000493</v>
+        <v>7000496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4726,7 +4721,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4739,9 +4734,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,7 +4762,7 @@
         <v>131292164</v>
       </c>
       <c r="B34" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>131292192</v>
       </c>
       <c r="B35" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>131292187</v>
       </c>
       <c r="B36" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>131292159</v>
       </c>
       <c r="B37" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>131292267</v>
       </c>
       <c r="B38" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>131292189</v>
       </c>
       <c r="B39" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -2341,7 +2341,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131292186</v>
+        <v>131292185</v>
       </c>
       <c r="B15" t="n">
         <v>79264</v>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528927</v>
+        <v>528965</v>
       </c>
       <c r="R15" t="n">
-        <v>7000496</v>
+        <v>7000595</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2415,11 +2415,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2467,7 +2462,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131292181</v>
+        <v>131292186</v>
       </c>
       <c r="B16" t="n">
         <v>79264</v>
@@ -2505,10 +2500,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528974</v>
+        <v>528927</v>
       </c>
       <c r="R16" t="n">
-        <v>7000525</v>
+        <v>7000496</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2545,7 +2540,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Särskilt rikligt med garnlav på en gammal gran.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2593,7 +2588,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131292185</v>
+        <v>131292181</v>
       </c>
       <c r="B17" t="n">
         <v>79264</v>
@@ -2631,10 +2626,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528965</v>
+        <v>528974</v>
       </c>
       <c r="R17" t="n">
-        <v>7000595</v>
+        <v>7000525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2667,6 +2662,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Särskilt rikligt med garnlav på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292163</v>
+        <v>131292263</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,29 +2725,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2757,10 +2756,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528921</v>
+        <v>528966</v>
       </c>
       <c r="R18" t="n">
-        <v>7000354</v>
+        <v>7000477</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2797,7 +2796,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2806,6 +2805,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2816,22 +2816,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292191</v>
+        <v>131292163</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2860,26 +2860,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528927</v>
+        <v>528921</v>
       </c>
       <c r="R19" t="n">
-        <v>7000340</v>
+        <v>7000354</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2927,7 +2932,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2936,7 +2941,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2955,9 +2959,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2975,10 +2984,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292265</v>
+        <v>131292191</v>
       </c>
       <c r="B20" t="n">
-        <v>79021</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2986,21 +2995,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3013,10 +3022,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529126</v>
+        <v>528927</v>
       </c>
       <c r="R20" t="n">
-        <v>7000447</v>
+        <v>7000340</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3051,6 +3060,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3064,6 +3078,21 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3081,10 +3110,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292263</v>
+        <v>131292265</v>
       </c>
       <c r="B21" t="n">
-        <v>80369</v>
+        <v>79021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,30 +3121,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3123,10 +3148,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528966</v>
+        <v>529126</v>
       </c>
       <c r="R21" t="n">
-        <v>7000477</v>
+        <v>7000447</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3161,11 +3186,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3179,26 +3199,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131292274</v>
+        <v>131292271</v>
       </c>
       <c r="B24" t="n">
         <v>79264</v>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528983</v>
+        <v>529122</v>
       </c>
       <c r="R24" t="n">
-        <v>7000463</v>
+        <v>7000459</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3730,7 +3730,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131292271</v>
+        <v>131292274</v>
       </c>
       <c r="B26" t="n">
         <v>79264</v>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529122</v>
+        <v>528983</v>
       </c>
       <c r="R26" t="n">
-        <v>7000459</v>
+        <v>7000463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131292170</v>
+        <v>131292190</v>
       </c>
       <c r="B27" t="n">
-        <v>80369</v>
+        <v>79264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3862,30 +3862,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3893,10 +3889,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528917</v>
+        <v>528945</v>
       </c>
       <c r="R27" t="n">
-        <v>7000532</v>
+        <v>7000349</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3931,6 +3927,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På flera granar i klenvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3943,27 +3944,22 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3981,10 +3977,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131292190</v>
+        <v>131292170</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>80369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3992,26 +3988,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528945</v>
+        <v>528917</v>
       </c>
       <c r="R28" t="n">
-        <v>7000349</v>
+        <v>7000532</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4057,11 +4057,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På flera granar i klenvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4074,22 +4069,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292249</v>
+        <v>131292264</v>
       </c>
       <c r="B29" t="n">
-        <v>83244</v>
+        <v>78276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,21 +4118,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528960</v>
+        <v>528951</v>
       </c>
       <c r="R29" t="n">
-        <v>7000493</v>
+        <v>7000496</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4208,9 +4208,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4228,10 +4233,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292166</v>
+        <v>131292249</v>
       </c>
       <c r="B30" t="n">
-        <v>57902</v>
+        <v>83244</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4239,31 +4244,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528920</v>
+        <v>528960</v>
       </c>
       <c r="R30" t="n">
-        <v>7000269</v>
+        <v>7000493</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4309,23 +4309,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4338,14 +4334,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4363,7 +4354,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292160</v>
+        <v>131292166</v>
       </c>
       <c r="B31" t="n">
         <v>57902</v>
@@ -4396,7 +4387,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4406,10 +4397,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528916</v>
+        <v>528920</v>
       </c>
       <c r="R31" t="n">
-        <v>7000358</v>
+        <v>7000269</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4446,7 +4437,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4460,7 +4451,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4498,7 +4489,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292157</v>
+        <v>131292160</v>
       </c>
       <c r="B32" t="n">
         <v>57902</v>
@@ -4531,7 +4522,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4541,10 +4532,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528904</v>
+        <v>528916</v>
       </c>
       <c r="R32" t="n">
-        <v>7000487</v>
+        <v>7000358</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4581,7 +4572,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4633,10 +4624,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292264</v>
+        <v>131292157</v>
       </c>
       <c r="B33" t="n">
-        <v>78276</v>
+        <v>57902</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4644,26 +4635,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4671,10 +4667,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528951</v>
+        <v>528904</v>
       </c>
       <c r="R33" t="n">
-        <v>7000496</v>
+        <v>7000487</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4709,13 +4705,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -1475,7 +1475,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292182</v>
+        <v>131292273</v>
       </c>
       <c r="B8" t="n">
         <v>79264</v>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528964</v>
+        <v>528941</v>
       </c>
       <c r="R8" t="n">
-        <v>7000504</v>
+        <v>7000481</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1549,11 +1549,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1601,7 +1596,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292184</v>
+        <v>131292188</v>
       </c>
       <c r="B9" t="n">
         <v>79264</v>
@@ -1639,10 +1634,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528962</v>
+        <v>528907</v>
       </c>
       <c r="R9" t="n">
-        <v>7000560</v>
+        <v>7000430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1679,7 +1674,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1707,9 +1702,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1727,7 +1727,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292188</v>
+        <v>131292184</v>
       </c>
       <c r="B10" t="n">
         <v>79264</v>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528907</v>
+        <v>528962</v>
       </c>
       <c r="R10" t="n">
-        <v>7000430</v>
+        <v>7000560</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1833,14 +1833,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1858,7 +1853,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292273</v>
+        <v>131292182</v>
       </c>
       <c r="B11" t="n">
         <v>79264</v>
@@ -1896,10 +1891,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528941</v>
+        <v>528964</v>
       </c>
       <c r="R11" t="n">
-        <v>7000481</v>
+        <v>7000504</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1932,6 +1927,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2462,7 +2462,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131292186</v>
+        <v>131292181</v>
       </c>
       <c r="B16" t="n">
         <v>79264</v>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528927</v>
+        <v>528974</v>
       </c>
       <c r="R16" t="n">
-        <v>7000496</v>
+        <v>7000525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Särskilt rikligt med garnlav på en gammal gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2588,7 +2588,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131292181</v>
+        <v>131292186</v>
       </c>
       <c r="B17" t="n">
         <v>79264</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528974</v>
+        <v>528927</v>
       </c>
       <c r="R17" t="n">
-        <v>7000525</v>
+        <v>7000496</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Särskilt rikligt med garnlav på en gammal gran.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292263</v>
+        <v>131292163</v>
       </c>
       <c r="B18" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,28 +2725,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2756,10 +2757,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528966</v>
+        <v>528921</v>
       </c>
       <c r="R18" t="n">
-        <v>7000477</v>
+        <v>7000354</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2796,7 +2797,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,7 +2806,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2816,22 +2816,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131292163</v>
+        <v>131292265</v>
       </c>
       <c r="B19" t="n">
-        <v>57902</v>
+        <v>79021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2860,31 +2860,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528921</v>
+        <v>529126</v>
       </c>
       <c r="R19" t="n">
-        <v>7000354</v>
+        <v>7000447</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2930,43 +2925,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2984,10 +2955,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131292191</v>
+        <v>131292263</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>80369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2995,26 +2966,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3022,10 +2997,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528927</v>
+        <v>528966</v>
       </c>
       <c r="R20" t="n">
-        <v>7000340</v>
+        <v>7000477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3062,7 +3037,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3082,17 +3057,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3110,10 +3090,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292265</v>
+        <v>131292191</v>
       </c>
       <c r="B21" t="n">
-        <v>79021</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3121,21 +3101,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3148,10 +3128,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529126</v>
+        <v>528927</v>
       </c>
       <c r="R21" t="n">
-        <v>7000447</v>
+        <v>7000340</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3186,6 +3166,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3199,6 +3184,21 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131292271</v>
+        <v>131292165</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3485,26 +3485,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3512,10 +3517,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529122</v>
+        <v>528924</v>
       </c>
       <c r="R24" t="n">
-        <v>7000459</v>
+        <v>7000345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3550,13 +3555,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3575,9 +3584,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3595,10 +3609,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131292165</v>
+        <v>131292271</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3606,31 +3620,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3638,10 +3647,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528924</v>
+        <v>529122</v>
       </c>
       <c r="R25" t="n">
-        <v>7000345</v>
+        <v>7000459</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3676,17 +3685,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3705,14 +3710,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131292190</v>
+        <v>131292170</v>
       </c>
       <c r="B27" t="n">
-        <v>79264</v>
+        <v>80369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3862,26 +3862,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3889,10 +3893,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528945</v>
+        <v>528917</v>
       </c>
       <c r="R27" t="n">
-        <v>7000349</v>
+        <v>7000532</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3927,11 +3931,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På flera granar i klenvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3944,22 +3943,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3977,10 +3981,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131292170</v>
+        <v>131292190</v>
       </c>
       <c r="B28" t="n">
-        <v>80369</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3988,30 +3992,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528917</v>
+        <v>528945</v>
       </c>
       <c r="R28" t="n">
-        <v>7000532</v>
+        <v>7000349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4057,6 +4057,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På flera granar i klenvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4069,27 +4074,22 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292264</v>
+        <v>131292249</v>
       </c>
       <c r="B29" t="n">
-        <v>78276</v>
+        <v>83244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,21 +4118,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528951</v>
+        <v>528960</v>
       </c>
       <c r="R29" t="n">
-        <v>7000496</v>
+        <v>7000493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4208,14 +4208,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4233,10 +4228,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292249</v>
+        <v>131292166</v>
       </c>
       <c r="B30" t="n">
-        <v>83244</v>
+        <v>57902</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4244,26 +4239,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528960</v>
+        <v>528920</v>
       </c>
       <c r="R30" t="n">
-        <v>7000493</v>
+        <v>7000269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4309,19 +4309,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4334,9 +4338,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4354,7 +4363,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292166</v>
+        <v>131292160</v>
       </c>
       <c r="B31" t="n">
         <v>57902</v>
@@ -4387,7 +4396,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4397,10 +4406,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528920</v>
+        <v>528916</v>
       </c>
       <c r="R31" t="n">
-        <v>7000269</v>
+        <v>7000358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4437,7 +4446,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4451,7 +4460,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4489,7 +4498,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292160</v>
+        <v>131292157</v>
       </c>
       <c r="B32" t="n">
         <v>57902</v>
@@ -4522,7 +4531,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4532,10 +4541,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528916</v>
+        <v>528904</v>
       </c>
       <c r="R32" t="n">
-        <v>7000358</v>
+        <v>7000487</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4572,7 +4581,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4624,10 +4633,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292157</v>
+        <v>131292264</v>
       </c>
       <c r="B33" t="n">
-        <v>57902</v>
+        <v>78276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4635,31 +4644,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4667,10 +4671,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528904</v>
+        <v>528951</v>
       </c>
       <c r="R33" t="n">
-        <v>7000487</v>
+        <v>7000496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4705,17 +4709,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292162</v>
+        <v>131292273</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,31 +1221,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1253,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528917</v>
+        <v>528941</v>
       </c>
       <c r="R6" t="n">
-        <v>7000356</v>
+        <v>7000481</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1291,23 +1286,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1320,14 +1311,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1345,10 +1331,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292254</v>
+        <v>131292188</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,31 +1342,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1388,10 +1369,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529159</v>
+        <v>528907</v>
       </c>
       <c r="R7" t="n">
-        <v>7000453</v>
+        <v>7000430</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1428,7 +1409,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,6 +1418,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1455,9 +1437,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1475,7 +1462,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292273</v>
+        <v>131292184</v>
       </c>
       <c r="B8" t="n">
         <v>79264</v>
@@ -1513,10 +1500,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528941</v>
+        <v>528962</v>
       </c>
       <c r="R8" t="n">
-        <v>7000481</v>
+        <v>7000560</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1549,6 +1536,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1596,7 +1588,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292188</v>
+        <v>131292182</v>
       </c>
       <c r="B9" t="n">
         <v>79264</v>
@@ -1634,10 +1626,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528907</v>
+        <v>528964</v>
       </c>
       <c r="R9" t="n">
-        <v>7000430</v>
+        <v>7000504</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1666,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1702,14 +1694,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1727,10 +1714,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292184</v>
+        <v>131292162</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,26 +1725,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1765,10 +1757,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528962</v>
+        <v>528917</v>
       </c>
       <c r="R10" t="n">
-        <v>7000560</v>
+        <v>7000356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1805,7 +1797,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,13 +1806,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1833,9 +1824,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1853,10 +1849,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292182</v>
+        <v>131292254</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1864,26 +1860,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1891,10 +1892,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528964</v>
+        <v>529159</v>
       </c>
       <c r="R11" t="n">
-        <v>7000504</v>
+        <v>7000453</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1931,7 +1932,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1940,7 +1941,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131292165</v>
+        <v>131292271</v>
       </c>
       <c r="B24" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3485,31 +3485,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3517,10 +3512,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528924</v>
+        <v>529122</v>
       </c>
       <c r="R24" t="n">
-        <v>7000345</v>
+        <v>7000459</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3555,17 +3550,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3584,14 +3575,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3609,7 +3595,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131292271</v>
+        <v>131292274</v>
       </c>
       <c r="B25" t="n">
         <v>79264</v>
@@ -3647,10 +3633,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529122</v>
+        <v>528983</v>
       </c>
       <c r="R25" t="n">
-        <v>7000459</v>
+        <v>7000463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3730,10 +3716,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131292274</v>
+        <v>131292165</v>
       </c>
       <c r="B26" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3741,26 +3727,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3768,10 +3759,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528983</v>
+        <v>528924</v>
       </c>
       <c r="R26" t="n">
-        <v>7000463</v>
+        <v>7000345</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3806,13 +3797,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3831,9 +3826,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292161</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292257</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131292153</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>131292255</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292273</v>
+        <v>131292162</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,26 +1221,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528941</v>
+        <v>528917</v>
       </c>
       <c r="R6" t="n">
-        <v>7000481</v>
+        <v>7000356</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,19 +1291,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1311,9 +1320,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1331,10 +1345,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292188</v>
+        <v>131292254</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,26 +1356,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1369,10 +1388,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528907</v>
+        <v>529159</v>
       </c>
       <c r="R7" t="n">
-        <v>7000430</v>
+        <v>7000453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1428,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,7 +1437,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1437,14 +1455,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,10 +1475,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292184</v>
+        <v>131292182</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528962</v>
+        <v>528964</v>
       </c>
       <c r="R8" t="n">
-        <v>7000560</v>
+        <v>7000504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,7 +1553,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1588,10 +1601,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292182</v>
+        <v>131292184</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528964</v>
+        <v>528962</v>
       </c>
       <c r="R9" t="n">
-        <v>7000504</v>
+        <v>7000560</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1666,7 +1679,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1714,10 +1727,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292162</v>
+        <v>131292188</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,31 +1738,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1757,10 +1765,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528917</v>
+        <v>528907</v>
       </c>
       <c r="R10" t="n">
-        <v>7000356</v>
+        <v>7000430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1797,7 +1805,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1806,12 +1814,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1826,12 +1835,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1849,10 +1858,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292254</v>
+        <v>131292273</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,31 +1869,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1892,10 +1896,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529159</v>
+        <v>528941</v>
       </c>
       <c r="R11" t="n">
-        <v>7000453</v>
+        <v>7000481</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1930,17 +1934,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>131292270</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131292183</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131292149</v>
       </c>
       <c r="B14" t="n">
-        <v>56716</v>
+        <v>56718</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131292185</v>
+        <v>131292186</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528965</v>
+        <v>528927</v>
       </c>
       <c r="R15" t="n">
-        <v>7000595</v>
+        <v>7000496</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2415,6 +2415,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2465,7 +2470,7 @@
         <v>131292181</v>
       </c>
       <c r="B16" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2588,10 +2593,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131292186</v>
+        <v>131292185</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,10 +2631,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528927</v>
+        <v>528965</v>
       </c>
       <c r="R17" t="n">
-        <v>7000496</v>
+        <v>7000595</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2662,11 +2667,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131292163</v>
+        <v>131292191</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,31 +2725,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2757,10 +2752,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528921</v>
+        <v>528927</v>
       </c>
       <c r="R18" t="n">
-        <v>7000354</v>
+        <v>7000340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2797,7 +2792,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2806,6 +2801,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2824,14 +2820,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2852,7 +2843,7 @@
         <v>131292265</v>
       </c>
       <c r="B19" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2958,7 +2949,7 @@
         <v>131292263</v>
       </c>
       <c r="B20" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3090,10 +3081,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131292191</v>
+        <v>131292163</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3101,26 +3092,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3128,10 +3124,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528927</v>
+        <v>528921</v>
       </c>
       <c r="R21" t="n">
-        <v>7000340</v>
+        <v>7000354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3168,7 +3164,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Ringhack, färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3177,7 +3173,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3196,9 +3191,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
         <v>131292256</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>131292260</v>
       </c>
       <c r="B23" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131292271</v>
+        <v>131292274</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529122</v>
+        <v>528983</v>
       </c>
       <c r="R24" t="n">
-        <v>7000459</v>
+        <v>7000463</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3595,10 +3595,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131292274</v>
+        <v>131292271</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528983</v>
+        <v>529122</v>
       </c>
       <c r="R25" t="n">
-        <v>7000463</v>
+        <v>7000459</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3719,7 +3719,7 @@
         <v>131292165</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>131292170</v>
       </c>
       <c r="B27" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>131292190</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>131292249</v>
       </c>
       <c r="B29" t="n">
-        <v>83244</v>
+        <v>83246</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292166</v>
+        <v>131292264</v>
       </c>
       <c r="B30" t="n">
-        <v>57902</v>
+        <v>78278</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4239,31 +4239,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4271,10 +4266,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528920</v>
+        <v>528951</v>
       </c>
       <c r="R30" t="n">
-        <v>7000269</v>
+        <v>7000496</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4309,23 +4304,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4340,12 +4331,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4363,10 +4354,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292160</v>
+        <v>131292166</v>
       </c>
       <c r="B31" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4396,7 +4387,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4406,10 +4397,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528916</v>
+        <v>528920</v>
       </c>
       <c r="R31" t="n">
-        <v>7000358</v>
+        <v>7000269</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4446,7 +4437,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4460,7 +4451,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4498,10 +4489,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292157</v>
+        <v>131292160</v>
       </c>
       <c r="B32" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4531,7 +4522,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4541,10 +4532,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528904</v>
+        <v>528916</v>
       </c>
       <c r="R32" t="n">
-        <v>7000487</v>
+        <v>7000358</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4581,7 +4572,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4633,10 +4624,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292264</v>
+        <v>131292157</v>
       </c>
       <c r="B33" t="n">
-        <v>78276</v>
+        <v>57904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4644,26 +4635,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4671,10 +4667,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528951</v>
+        <v>528904</v>
       </c>
       <c r="R33" t="n">
-        <v>7000496</v>
+        <v>7000487</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4709,13 +4705,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,7 +4762,7 @@
         <v>131292164</v>
       </c>
       <c r="B34" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>131292192</v>
       </c>
       <c r="B35" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>131292187</v>
       </c>
       <c r="B36" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>131292159</v>
       </c>
       <c r="B37" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>131292267</v>
       </c>
       <c r="B38" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>131292189</v>
       </c>
       <c r="B39" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 2316-2026 artfynd.xlsx
+++ b/artfynd/A 2316-2026 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131292162</v>
+        <v>131292182</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,31 +1221,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1253,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528917</v>
+        <v>528964</v>
       </c>
       <c r="R6" t="n">
-        <v>7000356</v>
+        <v>7000504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1293,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+          <t>På flera granar i barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,12 +1297,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1320,14 +1316,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1345,10 +1336,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131292254</v>
+        <v>131292184</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,31 +1347,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1388,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529159</v>
+        <v>528962</v>
       </c>
       <c r="R7" t="n">
-        <v>7000453</v>
+        <v>7000560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1428,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,6 +1423,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1475,7 +1462,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131292182</v>
+        <v>131292188</v>
       </c>
       <c r="B8" t="n">
         <v>79266</v>
@@ -1513,10 +1500,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528964</v>
+        <v>528907</v>
       </c>
       <c r="R8" t="n">
-        <v>7000504</v>
+        <v>7000430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1553,7 +1540,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På flera granar i barrblandskog.</t>
+          <t>I god mängd på en stående död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,9 +1568,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1601,7 +1593,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131292184</v>
+        <v>131292273</v>
       </c>
       <c r="B9" t="n">
         <v>79266</v>
@@ -1639,10 +1631,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528962</v>
+        <v>528941</v>
       </c>
       <c r="R9" t="n">
-        <v>7000560</v>
+        <v>7000481</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1675,11 +1667,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1727,10 +1714,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131292188</v>
+        <v>131292162</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,26 +1725,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1765,10 +1757,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528907</v>
+        <v>528917</v>
       </c>
       <c r="R10" t="n">
-        <v>7000430</v>
+        <v>7000356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1805,7 +1797,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I god mängd på en stående död gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,13 +1806,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1835,12 +1826,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1858,10 +1849,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292273</v>
+        <v>131292254</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,26 +1860,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1896,10 +1892,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528941</v>
+        <v>529159</v>
       </c>
       <c r="R11" t="n">
-        <v>7000481</v>
+        <v>7000453</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1934,13 +1930,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131292249</v>
+        <v>131292264</v>
       </c>
       <c r="B29" t="n">
-        <v>83246</v>
+        <v>78278</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,21 +4118,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528960</v>
+        <v>528951</v>
       </c>
       <c r="R29" t="n">
-        <v>7000493</v>
+        <v>7000496</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4208,9 +4208,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4228,10 +4233,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131292264</v>
+        <v>131292166</v>
       </c>
       <c r="B30" t="n">
-        <v>78278</v>
+        <v>57904</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4239,26 +4244,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4266,10 +4276,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528951</v>
+        <v>528920</v>
       </c>
       <c r="R30" t="n">
-        <v>7000496</v>
+        <v>7000269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4304,19 +4314,23 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4331,12 +4345,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4354,7 +4368,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131292166</v>
+        <v>131292160</v>
       </c>
       <c r="B31" t="n">
         <v>57904</v>
@@ -4387,7 +4401,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4397,10 +4411,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528920</v>
+        <v>528916</v>
       </c>
       <c r="R31" t="n">
-        <v>7000269</v>
+        <v>7000358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4437,7 +4451,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4451,7 +4465,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4489,7 +4503,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131292160</v>
+        <v>131292157</v>
       </c>
       <c r="B32" t="n">
         <v>57904</v>
@@ -4522,7 +4536,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4532,10 +4546,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528916</v>
+        <v>528904</v>
       </c>
       <c r="R32" t="n">
-        <v>7000358</v>
+        <v>7000487</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4572,7 +4586,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4624,10 +4638,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131292157</v>
+        <v>131292249</v>
       </c>
       <c r="B33" t="n">
-        <v>57904</v>
+        <v>83246</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4635,31 +4649,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4667,10 +4676,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528904</v>
+        <v>528960</v>
       </c>
       <c r="R33" t="n">
-        <v>7000487</v>
+        <v>7000493</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4705,23 +4714,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant nära en bäck.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4734,14 +4739,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
